--- a/src/attributions/attributions_saliency_traj_238.xlsx
+++ b/src/attributions/attributions_saliency_traj_238.xlsx
@@ -999,571 +999,571 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.3047280609607697</v>
+        <v>0.2767753303050995</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04031389951705933</v>
+        <v>0.1640193313360214</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03484270349144936</v>
+        <v>0.1809414625167847</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03803393244743347</v>
+        <v>0.04862925410270691</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1936643421649933</v>
+        <v>0.01178281754255295</v>
       </c>
       <c r="F2" t="n">
-        <v>0.009654183872044086</v>
+        <v>0.1726098358631134</v>
       </c>
       <c r="G2" t="n">
-        <v>0.09138882905244827</v>
+        <v>0.1701816320419312</v>
       </c>
       <c r="H2" t="n">
-        <v>0.03854655846953392</v>
+        <v>0.05149184539914131</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02979231439530849</v>
+        <v>0.1242443174123764</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3371071815490723</v>
+        <v>0.3283102512359619</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02615870162844658</v>
+        <v>0.206525444984436</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003512779250741005</v>
+        <v>0.1262728720903397</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01957922987639904</v>
+        <v>0.1195421367883682</v>
       </c>
       <c r="N2" t="n">
-        <v>0.204264372587204</v>
+        <v>0.05995742976665497</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01070056762546301</v>
+        <v>0.2022953033447266</v>
       </c>
       <c r="P2" t="n">
-        <v>0.04858287796378136</v>
+        <v>0.1656410694122314</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01438765227794647</v>
+        <v>0.04493030905723572</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01818365231156349</v>
+        <v>0.09960293024778366</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0134844733402133</v>
+        <v>0.1085246205329895</v>
       </c>
       <c r="T2" t="n">
-        <v>0.03386763110756874</v>
+        <v>0.05784479528665543</v>
       </c>
       <c r="U2" t="n">
-        <v>0.00190241273958236</v>
+        <v>0.07174106687307358</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0312100388109684</v>
+        <v>0.1642878949642181</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01202838867902756</v>
+        <v>0.0628964900970459</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01732169650495052</v>
+        <v>0.2099173069000244</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.008852339349687099</v>
+        <v>0.004659822210669518</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.05650408938527107</v>
+        <v>0.1219811514019966</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01234558690339327</v>
+        <v>0.04858934134244919</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0009872745722532272</v>
+        <v>0.1085720807313919</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.03018476068973541</v>
+        <v>0.1373482644557953</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.005935279652476311</v>
+        <v>0.009198758751153946</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.005941956304013729</v>
+        <v>0.009208463132381439</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.007891359739005566</v>
+        <v>0.1080310493707657</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.02192851714789867</v>
+        <v>0.02164057642221451</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.03809833154082298</v>
+        <v>0.009458731859922409</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.05072062462568283</v>
+        <v>0.07574380934238434</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.001647663535550237</v>
+        <v>0.02433397993445396</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.07609082013368607</v>
+        <v>0.1383996605873108</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.01023329515010118</v>
+        <v>0.03303880244493484</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.01792779564857483</v>
+        <v>0.06611482799053192</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.04721303656697273</v>
+        <v>0.08159861713647842</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.01193089783191681</v>
+        <v>0.1076772809028625</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.0150627950206399</v>
+        <v>0.05926266685128212</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.01459065452218056</v>
+        <v>0.07241114974021912</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.03733907639980316</v>
+        <v>0.03508397936820984</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.004759388510137796</v>
+        <v>0.05358473211526871</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.1469779312610626</v>
+        <v>0.2509615421295166</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.02418005280196667</v>
+        <v>0.1690846234560013</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.04445551708340645</v>
+        <v>0.1448520720005035</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.014552878215909</v>
+        <v>0.05986245349049568</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.1680318862199783</v>
+        <v>0.1581544280052185</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.03448010981082916</v>
+        <v>0.1584905683994293</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.009740606881678104</v>
+        <v>0.04946636408567429</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.05622608959674835</v>
+        <v>0.03722206130623817</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.001396307488903403</v>
+        <v>0.07046075165271759</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.09451810270547867</v>
+        <v>0.07298371940851212</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.05566703900694847</v>
+        <v>0.04301485791802406</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.05233917757868767</v>
+        <v>0.1231801807880402</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.06563108414411545</v>
+        <v>0.02029262483119965</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.00398848345503211</v>
+        <v>0.2104528099298477</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.003172060009092093</v>
+        <v>0.2880558669567108</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.0106057757511735</v>
+        <v>0.103179007768631</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.02054981514811516</v>
+        <v>0.1300736516714096</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.03784701228141785</v>
+        <v>0.01460402831435204</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.01785924285650253</v>
+        <v>0.1049935668706894</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.01570795103907585</v>
+        <v>0.04678551852703094</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.01678985357284546</v>
+        <v>0.02421306073665619</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.0401427298784256</v>
+        <v>0.04857973009347916</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.03175514191389084</v>
+        <v>0.02995527535676956</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.01660769246518612</v>
+        <v>0.0203575175255537</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.01994584314525127</v>
+        <v>0.06478719413280487</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.01234506256878376</v>
+        <v>0.1825229674577713</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.008973845280706882</v>
+        <v>0.007971075363457203</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.09240546822547913</v>
+        <v>0.2140769213438034</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.00760707026347518</v>
+        <v>0.03578274697065353</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.03561124205589294</v>
+        <v>0.06139890104532242</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.009914588183164597</v>
+        <v>0.08949333429336548</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.07494331896305084</v>
+        <v>0.2035432755947113</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.01557077839970589</v>
+        <v>0.1277227699756622</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.006886946968734264</v>
+        <v>0.03096441179513931</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.06626276671886444</v>
+        <v>0.1665187329053879</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.01478472072631121</v>
+        <v>0.05390480160713196</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.05614565685391426</v>
+        <v>0.0645475909113884</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.01830398105084896</v>
+        <v>0.02701068297028542</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.003945534583181143</v>
+        <v>0.03054494969546795</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.01163965277373791</v>
+        <v>0.03642009571194649</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.03315668925642967</v>
+        <v>0.01552367489784956</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.01095587480813265</v>
+        <v>0.02063366770744324</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.01366464607417583</v>
+        <v>0.002146858721971512</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.03843182325363159</v>
+        <v>0.01948234438896179</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.0008912574267014861</v>
+        <v>0.02075032331049442</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.006383052561432123</v>
+        <v>0.02767142094671726</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.01890894211828709</v>
+        <v>0.03376295417547226</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.03185372799634933</v>
+        <v>0.1203365251421928</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.034366674721241</v>
+        <v>0.03732920438051224</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.002081248443573713</v>
+        <v>0.4145531058311462</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.02082573436200619</v>
+        <v>0.340567946434021</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.06345541775226593</v>
+        <v>0.03197887912392616</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.04495398327708244</v>
+        <v>0.1057885959744453</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.01833763718605042</v>
+        <v>0.06930538266897202</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.0497884601354599</v>
+        <v>0.07668102532625198</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.01071661338210106</v>
+        <v>0.001946975477039814</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.005831078160554171</v>
+        <v>0.03505624085664749</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.008505631238222122</v>
+        <v>0.01014710403978825</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.03310156241059303</v>
+        <v>0.03523653745651245</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.01091929990798235</v>
+        <v>0.02704117819666862</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.03117059171199799</v>
+        <v>0.02183462679386139</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.02672149054706097</v>
+        <v>0.007537723518908024</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.004582919180393219</v>
+        <v>0.01027808990329504</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.0102551281452179</v>
+        <v>0.09311546385288239</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.01411409862339497</v>
+        <v>0.2239075750112534</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.0171729139983654</v>
+        <v>0.0240480899810791</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.05114022642374039</v>
+        <v>0.05492307245731354</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.05525059998035431</v>
+        <v>0.05584291368722916</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.01020468212664127</v>
+        <v>0.1705121695995331</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.01820040866732597</v>
+        <v>0.01138196513056755</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.06887609511613846</v>
+        <v>0.02261186949908733</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.03925766423344612</v>
+        <v>0.1165784001350403</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.004362276755273342</v>
+        <v>0.003413405269384384</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.005339668598026037</v>
+        <v>0.1425847709178925</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.02206104435026646</v>
+        <v>0.07460559159517288</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.01555200666189194</v>
+        <v>0.05559461191296577</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.002447612583637238</v>
+        <v>0.03311194479465485</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.0346430130302906</v>
+        <v>0.1133354157209396</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.005494819022715092</v>
+        <v>0.01543864980340004</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.05907269567251205</v>
+        <v>0.1000440716743469</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.01249098684638739</v>
+        <v>0.09792385250329971</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.007022696081548929</v>
+        <v>0.0366622731089592</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.00440323119983077</v>
+        <v>0.1162912249565125</v>
       </c>
       <c r="DY2" t="n">
-        <v>7.929117418825626e-05</v>
+        <v>0.09825801849365234</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.003823204431682825</v>
+        <v>0.3422691226005554</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.01078879274427891</v>
+        <v>0.3351885378360748</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.006007042713463306</v>
+        <v>0.02191013470292091</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.0145572405308485</v>
+        <v>0.1206132769584656</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.02360304445028305</v>
+        <v>0.08073212206363678</v>
       </c>
       <c r="EE2" t="n">
-        <v>0.01241779141128063</v>
+        <v>0.07640561461448669</v>
       </c>
       <c r="EF2" t="n">
-        <v>0.06589038670063019</v>
+        <v>0.05777060613036156</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.01650291681289673</v>
+        <v>0.05041270330548286</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.007359249051660299</v>
+        <v>0.07156015932559967</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.0002420265227556229</v>
+        <v>0.002070375718176365</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.03238760679960251</v>
+        <v>0.1205234304070473</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.005681025795638561</v>
+        <v>0.04886451363563538</v>
       </c>
       <c r="EL2" t="n">
-        <v>0.001080001471564174</v>
+        <v>0.05909064039587975</v>
       </c>
       <c r="EM2" t="n">
-        <v>0.02750277332961559</v>
+        <v>0.02176541090011597</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.005023045465350151</v>
+        <v>0.06044327467679977</v>
       </c>
       <c r="EO2" t="n">
-        <v>0.02438493445515633</v>
+        <v>0.06461107730865479</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.03404048457741737</v>
+        <v>0.09503631293773651</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0.02061543613672256</v>
+        <v>0.06604377925395966</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.01742257736623287</v>
+        <v>0.04158786684274673</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.05396681278944016</v>
+        <v>0.004487661644816399</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.01812233589589596</v>
+        <v>0.008813443593680859</v>
       </c>
       <c r="EU2" t="n">
-        <v>0.05734897032380104</v>
+        <v>0.03056769073009491</v>
       </c>
       <c r="EV2" t="n">
-        <v>0.008971855975687504</v>
+        <v>0.05141515284776688</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.007962034083902836</v>
+        <v>0.02703799493610859</v>
       </c>
       <c r="EX2" t="n">
-        <v>0.04686656966805458</v>
+        <v>0.07470129430294037</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.01209345553070307</v>
+        <v>0.01335727982223034</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0.001415698789060116</v>
+        <v>0.01029137521982193</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.01176196616142988</v>
+        <v>0.04698605090379715</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.03028561174869537</v>
+        <v>0.04881805554032326</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.01387646608054638</v>
+        <v>0.001946550793945789</v>
       </c>
       <c r="FD2" t="n">
-        <v>0.01326046604663134</v>
+        <v>0.02975822798907757</v>
       </c>
       <c r="FE2" t="n">
-        <v>0.04156066849827766</v>
+        <v>0.004537388682365417</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.002431974280625582</v>
+        <v>0.02219323813915253</v>
       </c>
       <c r="FG2" t="n">
-        <v>0.04069139435887337</v>
+        <v>0.05893463641405106</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.02363085560500622</v>
+        <v>0.02498214319348335</v>
       </c>
       <c r="FI2" t="n">
-        <v>0.0111994156613946</v>
+        <v>0.1201280727982521</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.03232435882091522</v>
+        <v>0.1297995150089264</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.02520651742815971</v>
+        <v>0.1751696318387985</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.008918724954128265</v>
+        <v>0.1624355614185333</v>
       </c>
       <c r="FM2" t="n">
-        <v>0.00545360054820776</v>
+        <v>0.1386583000421524</v>
       </c>
       <c r="FN2" t="n">
-        <v>0.01755297742784023</v>
+        <v>0.09067561477422714</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.009872265160083771</v>
+        <v>0.1195736825466156</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.06851372122764587</v>
+        <v>0.1104578673839569</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.07946062088012695</v>
+        <v>0.248938649892807</v>
       </c>
       <c r="FR2" t="n">
-        <v>0.01578042283654213</v>
+        <v>0.1535413861274719</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.03372898697853088</v>
+        <v>0.4918966591358185</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.02944321744143963</v>
+        <v>0.1551346182823181</v>
       </c>
       <c r="FU2" t="n">
-        <v>0.01128576509654522</v>
+        <v>0.1219343319535255</v>
       </c>
       <c r="FV2" t="n">
-        <v>0.05095010623335838</v>
+        <v>0.04911421239376068</v>
       </c>
       <c r="FW2" t="n">
-        <v>0.004262912087142467</v>
+        <v>0.1645398736000061</v>
       </c>
       <c r="FX2" t="n">
-        <v>0.01024270430207253</v>
+        <v>0.1349416524171829</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.02703236974775791</v>
+        <v>0.04021197929978371</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.01690181903541088</v>
+        <v>0.05479639768600464</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.02049661055207253</v>
+        <v>0.1586790233850479</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.04715245962142944</v>
+        <v>0.05083879828453064</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.06295207142829895</v>
+        <v>0.1033953726291656</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.02756733074784279</v>
+        <v>0.07348538190126419</v>
       </c>
       <c r="GE2" t="n">
-        <v>0.0005693255225196481</v>
+        <v>0.0006977394223213196</v>
       </c>
       <c r="GF2" t="n">
-        <v>0.015984071418643</v>
+        <v>0.08828255534172058</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.02051505818963051</v>
+        <v>0.09693944454193115</v>
       </c>
     </row>
     <row r="3">
@@ -2137,571 +2137,571 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.004332595970481634</v>
+        <v>0.000497177301440388</v>
       </c>
       <c r="B4" t="n">
-        <v>0.04557536914944649</v>
+        <v>0.0009907258208841085</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002068584784865379</v>
+        <v>5.228481313679367e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005134433973580599</v>
+        <v>0.0001978890795726329</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001454245066270232</v>
+        <v>3.177254984620959e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03325117751955986</v>
+        <v>0.0004481335927266628</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002673273906111717</v>
+        <v>0.0001234730589203537</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002291833283379674</v>
+        <v>0.0001783941406756639</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01907985657453537</v>
+        <v>9.114566637435928e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>0.006009974516928196</v>
+        <v>0.0003868757048621774</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0472227931022644</v>
+        <v>0.001078865374438465</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0004912731237709522</v>
+        <v>3.822736471192911e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>0.009921425022184849</v>
+        <v>0.0003425513859838247</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01179980114102364</v>
+        <v>0.0001775114797055721</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02495125308632851</v>
+        <v>0.0005383197567425668</v>
       </c>
       <c r="P4" t="n">
-        <v>0.004607814829796553</v>
+        <v>4.404694209370064e-06</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0001189019531011581</v>
+        <v>1.47789905895479e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>0.009500080719590187</v>
+        <v>0.0003006355836987495</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0009323079138994217</v>
+        <v>6.207813567016274e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001775504788383842</v>
+        <v>2.161769407393876e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>0.008918718434870243</v>
+        <v>0.0001147811417467892</v>
       </c>
       <c r="V4" t="n">
-        <v>0.002356254495680332</v>
+        <v>0.000139389987452887</v>
       </c>
       <c r="W4" t="n">
-        <v>0.005548353306949139</v>
+        <v>0.0001951505546458066</v>
       </c>
       <c r="X4" t="n">
-        <v>0.007009109016507864</v>
+        <v>0.0001336900750175118</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.001386214746162295</v>
+        <v>0.0001216362798004411</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0008794319583103061</v>
+        <v>0.0002364195679547265</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0008622009190730751</v>
+        <v>5.535834134207107e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.003445598529651761</v>
+        <v>0.0001296305417781696</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.001905561191961169</v>
+        <v>7.653265492990613e-05</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.007849929854273796</v>
+        <v>3.855650356854312e-05</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.002301850356161594</v>
+        <v>0.0003372691862750798</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.004791352897882462</v>
+        <v>0.0004327036440372467</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.002059917664155364</v>
+        <v>0.0001059813293977641</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.000542035442776978</v>
+        <v>4.986183193977922e-05</v>
       </c>
       <c r="AI4" t="n">
-        <v>9.760569082573056e-05</v>
+        <v>0.0002341848448850214</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.00318119814619422</v>
+        <v>4.022236680611968e-06</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.007665263954550028</v>
+        <v>0.000148803141200915</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.003193533513695002</v>
+        <v>0.0001929160789586604</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.01163969561457634</v>
+        <v>0.0001288137282244861</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.0004677952383644879</v>
+        <v>0.0001795181742636487</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.004636982455849648</v>
+        <v>3.940464375773445e-05</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.003690420184284449</v>
+        <v>9.026075713336468e-05</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.003660670015960932</v>
+        <v>0.0001818595046643168</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.004004308953881264</v>
+        <v>0.0001000159973045811</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.002545757917687297</v>
+        <v>6.967721856199205e-05</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.873397458344698e-05</v>
+        <v>0.0002760144707281142</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.03786615654826164</v>
+        <v>0.0006595367449335754</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.01561802439391613</v>
+        <v>0.0001023775985231623</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.002667334629222751</v>
+        <v>7.984583135112189e-06</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.009186467155814171</v>
+        <v>0.0003481046878732741</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.009752935729920864</v>
+        <v>0.00021222977375146</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.004050018265843391</v>
+        <v>2.348598536627833e-05</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.004740250762552023</v>
+        <v>8.905869617592543e-05</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.01146756298840046</v>
+        <v>0.0001191724513773806</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.005448142532259226</v>
+        <v>8.340876229340211e-05</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.0134234894067049</v>
+        <v>0.0002450025349389762</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.006549826823174953</v>
+        <v>0.0001056753026205115</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.001750897848978639</v>
+        <v>0.0001552411704324186</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.003058173228055239</v>
+        <v>0.0002059123362414539</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.0221325121819973</v>
+        <v>0.0001634483051020652</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.0005219071172177792</v>
+        <v>1.358762710879091e-05</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.004725469276309013</v>
+        <v>8.647640788694844e-05</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.007307708729058504</v>
+        <v>5.840191079187207e-05</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.006962165702134371</v>
+        <v>5.41951521881856e-05</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.005412451922893524</v>
+        <v>5.074969521956518e-05</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.003590327687561512</v>
+        <v>2.22660819417797e-05</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.008139690384268761</v>
+        <v>7.713000741205178e-06</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.00519825192168355</v>
+        <v>0.0001529294240754098</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.001381882466375828</v>
+        <v>3.188210030202754e-06</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.007752676960080862</v>
+        <v>0.0002412511821603402</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.006167997606098652</v>
+        <v>0.0001007895989459939</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.002269637538120151</v>
+        <v>0.000193101484910585</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.002384784631431103</v>
+        <v>0.0001719440624583513</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.01929259859025478</v>
+        <v>0.0004425219667609781</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.01060118712484837</v>
+        <v>8.453232294414192e-05</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.001117450417950749</v>
+        <v>7.091971929185092e-05</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.007226164918392897</v>
+        <v>2.905726614699233e-05</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.002470838138833642</v>
+        <v>0.0003081558388657868</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.002558009466156363</v>
+        <v>0.0001224942388944328</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.003695037681609392</v>
+        <v>1.395784056512639e-05</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.004159695468842983</v>
+        <v>9.797529492061585e-05</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.0005769897252321243</v>
+        <v>0.0001327130303252488</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.00648847920820117</v>
+        <v>0.0002875448844861239</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.002379060722887516</v>
+        <v>3.757347076316364e-05</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.0009502639295533299</v>
+        <v>6.420809950213879e-05</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.0003007575869560242</v>
+        <v>1.525911466160323e-05</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.007958501577377319</v>
+        <v>0.0001442213251721114</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.001711237942799926</v>
+        <v>6.5075364545919e-05</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.002344937063753605</v>
+        <v>3.946408469346352e-05</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.0003604552475735545</v>
+        <v>6.148509419290349e-05</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.006553803570568562</v>
+        <v>8.61642838572152e-05</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.01176016684621572</v>
+        <v>0.0004023904039058834</v>
       </c>
       <c r="CO4" t="n">
-        <v>7.225701119750738e-05</v>
+        <v>0.000167109610629268</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.0099048912525177</v>
+        <v>0.0001948688150150701</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.003590033389627934</v>
+        <v>0.0001142842302215286</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.001639897469431162</v>
+        <v>0.0002491397317498922</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.002028657123446465</v>
+        <v>4.157428702455945e-05</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.01005290262401104</v>
+        <v>1.992935358430259e-05</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.005812232382595539</v>
+        <v>3.575628943508491e-05</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.001005261554382741</v>
+        <v>0.0001007785831461661</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.006721798796206713</v>
+        <v>0.000268845702521503</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.003025031415745616</v>
+        <v>3.72120994143188e-05</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.0006897243438288569</v>
+        <v>6.33782910881564e-05</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.00123816542327404</v>
+        <v>8.795304893283173e-06</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.007336150389164686</v>
+        <v>0.000144752993946895</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.0008133244118653238</v>
+        <v>1.787985820556059e-05</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.001077879220247269</v>
+        <v>0.000105747785710264</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.001807574881240726</v>
+        <v>4.772508691530675e-05</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.001120034838095307</v>
+        <v>6.974725692998618e-05</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.004599334672093391</v>
+        <v>0.0001363488263450563</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.005346352234482765</v>
+        <v>8.844570402288809e-05</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.005532151088118553</v>
+        <v>0.0001041132127284072</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.02240375243127346</v>
+        <v>0.0004656571545638144</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.009221388958394527</v>
+        <v>5.334072193363681e-05</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.001318954396992922</v>
+        <v>8.855258784024045e-05</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.0006770773325115442</v>
+        <v>4.594936763169244e-05</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.00745824072510004</v>
+        <v>2.32234742725268e-05</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.0008437016513198614</v>
+        <v>2.494600812497083e-05</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.001058786874637008</v>
+        <v>0.0001702383597148582</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.001658661756664515</v>
+        <v>8.203776087611914e-05</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.001766190747730434</v>
+        <v>1.608569982636254e-05</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.0007334515685215592</v>
+        <v>0.0001130664386437275</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.006357345730066299</v>
+        <v>0.0001349358935840428</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.003760706866160035</v>
+        <v>4.956410703016445e-05</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.007235702592879534</v>
+        <v>0.0002043908752966672</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.003977903630584478</v>
+        <v>8.037364750634879e-05</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.001633896376006305</v>
+        <v>0.0001337828289251775</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.001348861260339618</v>
+        <v>7.801291940268129e-05</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.008048247545957565</v>
+        <v>7.625604484928772e-05</v>
       </c>
       <c r="DZ4" t="n">
-        <v>8.590953075326979e-05</v>
+        <v>0.0001625045260880142</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.001669641816988587</v>
+        <v>2.617781865410507e-05</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.001902526244521141</v>
+        <v>2.692169800866395e-05</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.0006108264205977321</v>
+        <v>6.186847167555243e-05</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.008488466963171959</v>
+        <v>0.0001644414151087403</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.001610299339517951</v>
+        <v>0.0001573153131175786</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.0009767094161361456</v>
+        <v>8.037818770390004e-05</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.008728770539164543</v>
+        <v>7.595647184643894e-05</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.003455889644101262</v>
+        <v>0.000129316802485846</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.002975743496790528</v>
+        <v>2.479624527040869e-05</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.003333022585138679</v>
+        <v>5.822060484206304e-05</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.00396735081449151</v>
+        <v>4.501911462284625e-05</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.0004972415044903755</v>
+        <v>9.346197657578159e-06</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.001369893783703446</v>
+        <v>6.5422966144979e-05</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.0002445206046104431</v>
+        <v>2.534292798372917e-05</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.002856676001101732</v>
+        <v>0.0001579585659783334</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.006661972962319851</v>
+        <v>0.0001485846441937611</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.008117130026221275</v>
+        <v>8.370006980840117e-05</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.004895655438303947</v>
+        <v>4.102622551727109e-05</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.00724893668666482</v>
+        <v>0.0001364863128401339</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.004936326760798693</v>
+        <v>0.0002318762126378715</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.0008949234616011381</v>
+        <v>5.881217657588422e-05</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.007191536016762257</v>
+        <v>1.938131936185528e-05</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.0004250943893566728</v>
+        <v>0.0001677699765423313</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.001184721826575696</v>
+        <v>0.0001368145749438554</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.005598053801804781</v>
+        <v>0.0003118870372418314</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.004290910437703133</v>
+        <v>2.706147643039003e-05</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.002337150741368532</v>
+        <v>7.521735096815974e-05</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.003520624246448278</v>
+        <v>5.290461558615789e-05</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.006957489531487226</v>
+        <v>0.0001207131426781416</v>
       </c>
       <c r="FD4" t="n">
-        <v>6.724891863996163e-05</v>
+        <v>5.759516352554783e-05</v>
       </c>
       <c r="FE4" t="n">
-        <v>0.002974599599838257</v>
+        <v>6.958597805351019e-05</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.001253393245860934</v>
+        <v>1.105854607885703e-07</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.0003052386164199561</v>
+        <v>3.121550980722532e-05</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.001481674029491842</v>
+        <v>0.0002416376955807209</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.008997155353426933</v>
+        <v>9.612459689378738e-05</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.003158151404932141</v>
+        <v>0.000104332051705569</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.003392732003703713</v>
+        <v>1.402305861120112e-05</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.003312076907604933</v>
+        <v>0.0002944599254988134</v>
       </c>
       <c r="FM4" t="n">
-        <v>0.006420857273042202</v>
+        <v>0.0001065683682099916</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.002122186124324799</v>
+        <v>0.0001735864789225161</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.002240837784484029</v>
+        <v>0.0001501623191870749</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.006900821346789598</v>
+        <v>0.0002200357266701758</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.0186060257256031</v>
+        <v>0.0003007842460647225</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.007456565741449594</v>
+        <v>0.0002396483323536813</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.002906216774135828</v>
+        <v>0.0002042601845460013</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.01034817285835743</v>
+        <v>4.227396857459098e-05</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.007902496494352818</v>
+        <v>0.0002046588779194281</v>
       </c>
       <c r="FV4" t="n">
-        <v>0.0006716404459439218</v>
+        <v>0.000152686785440892</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.004067810252308846</v>
+        <v>0.0001171329131466337</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.006788077764213085</v>
+        <v>7.667350291740149e-05</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.002921759383752942</v>
+        <v>0.0001542521931696683</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.008426560088992119</v>
+        <v>9.162269634543918e-06</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.002793459920212626</v>
+        <v>0.0001333837280981243</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.003830451285466552</v>
+        <v>3.236856355215423e-05</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.003360183676704764</v>
+        <v>4.930634895572439e-05</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.001295091700740159</v>
+        <v>0.0001556016504764557</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.002892371267080307</v>
+        <v>0.0001063380914274603</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.003476674202829599</v>
+        <v>7.521413499489427e-05</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.003221580758690834</v>
+        <v>0.0001614590146346018</v>
       </c>
     </row>
     <row r="5">
@@ -3275,2278 +3275,2278 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.05682545155286789</v>
+        <v>0.0008629723452031612</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1778480708599091</v>
+        <v>0.0290176048874855</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02882407605648041</v>
+        <v>0.009010907262563705</v>
       </c>
       <c r="D6" t="n">
-        <v>0.07243053615093231</v>
+        <v>0.008417441509664059</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1388911306858063</v>
+        <v>0.01441059168428183</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2831272780895233</v>
+        <v>0.0302906259894371</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01707099750638008</v>
+        <v>0.005917023867368698</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1256091892719269</v>
+        <v>0.02867919020354748</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02301723882555962</v>
+        <v>0.006437771022319794</v>
       </c>
       <c r="J6" t="n">
-        <v>0.04071518033742905</v>
+        <v>0.005577402655035257</v>
       </c>
       <c r="K6" t="n">
-        <v>0.157675638794899</v>
+        <v>0.03020642325282097</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01566549763083458</v>
+        <v>0.007516949903219938</v>
       </c>
       <c r="M6" t="n">
-        <v>0.04450316354632378</v>
+        <v>0.004176593385636806</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01909970119595528</v>
+        <v>0.02532949112355709</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1925966292619705</v>
+        <v>0.02570188231766224</v>
       </c>
       <c r="P6" t="n">
-        <v>0.005726564675569534</v>
+        <v>0.001574170310050249</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1244897171854973</v>
+        <v>0.02872938849031925</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01785809360444546</v>
+        <v>0.007676662877202034</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001795703545212746</v>
+        <v>0.0003810101188719273</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01275112479925156</v>
+        <v>0.008792649023234844</v>
       </c>
       <c r="U6" t="n">
-        <v>0.03684240207076073</v>
+        <v>0.002247643191367388</v>
       </c>
       <c r="V6" t="n">
-        <v>0.05456916987895966</v>
+        <v>0.007272152230143547</v>
       </c>
       <c r="W6" t="n">
-        <v>0.05847299844026566</v>
+        <v>0.009294466115534306</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0293225534260273</v>
+        <v>0.001107085729017854</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.02774848975241184</v>
+        <v>0.0006462461897172034</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.02060374990105629</v>
+        <v>0.007021822966635227</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01525207795202732</v>
+        <v>0.0001859710901044309</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.009538559243083</v>
+        <v>0.003407099982723594</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.01228675618767738</v>
+        <v>0.003508815774694085</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.02206330001354218</v>
+        <v>0.002761607524007559</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.01054434478282928</v>
+        <v>0.01772623136639595</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.02415727078914642</v>
+        <v>0.01996613293886185</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.04265116900205612</v>
+        <v>0.003308098996058106</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.06491079926490784</v>
+        <v>0.003720198292285204</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.02428130619227886</v>
+        <v>0.006857987493276596</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.01154171209782362</v>
+        <v>0.003660010639578104</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.001988187897950411</v>
+        <v>0.005516989156603813</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.02578816562891006</v>
+        <v>0.0009691861341707408</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.01680545322597027</v>
+        <v>0.004191785585135221</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.02088894136250019</v>
+        <v>0.004138510674238205</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.02549132332205772</v>
+        <v>0.01426036469638348</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.05350480973720551</v>
+        <v>0.0106621365994215</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.009018277749419212</v>
+        <v>0.007505096029490232</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.03945964202284813</v>
+        <v>0.01063564978539944</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.01537918113172054</v>
+        <v>0.004161101300269365</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.03934388980269432</v>
+        <v>0.001564144622534513</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.07111622393131256</v>
+        <v>0.03355866298079491</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.005564356222748756</v>
+        <v>0.002356000477448106</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.007671937812119722</v>
+        <v>0.001235631061717868</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.1257829517126083</v>
+        <v>0.005314176436513662</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.18775774538517</v>
+        <v>0.005616571754217148</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.02473589032888412</v>
+        <v>0.001701284432783723</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.04729054123163223</v>
+        <v>0.005682859569787979</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.03630604967474937</v>
+        <v>0.009651108644902706</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.0006809118203818798</v>
+        <v>0.009142541326582432</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.05558447167277336</v>
+        <v>0.0284876823425293</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.01420206762850285</v>
+        <v>0.009292840957641602</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.06256277114152908</v>
+        <v>0.005167568102478981</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.06577668339014053</v>
+        <v>0.03572818636894226</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.03416493535041809</v>
+        <v>0.00231461483053863</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.01778142899274826</v>
+        <v>0.002999154385179281</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.01312025636434555</v>
+        <v>0.001812059432268143</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.004913298413157463</v>
+        <v>0.002525509800761938</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.01623384095728397</v>
+        <v>0.001927363104186952</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.0488894097507</v>
+        <v>0.001072747632861137</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.02796261385083199</v>
+        <v>0.009044567123055458</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.00309328967705369</v>
+        <v>0.007261366117745638</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.02100195549428463</v>
+        <v>0.005178272724151611</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.00157866720110178</v>
+        <v>0.001785632222890854</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.03878005966544151</v>
+        <v>0.0007987776771187782</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.0468849316239357</v>
+        <v>0.009562671184539795</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.03022138401865959</v>
+        <v>0.001514423754997551</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.02647718600928783</v>
+        <v>0.005632648710161448</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.06050632148981094</v>
+        <v>0.02557249367237091</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.01233845204114914</v>
+        <v>0.0005975216627120972</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.01671218313276768</v>
+        <v>0.002688374603167176</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.05039926618337631</v>
+        <v>0.008848417550325394</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.06076430901885033</v>
+        <v>0.01037450321018696</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.006646266207098961</v>
+        <v>0.009843443520367146</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.04142624884843826</v>
+        <v>0.003007913241162896</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.01988357119262218</v>
+        <v>0.0006244602845981717</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.0005382769741117954</v>
+        <v>0.00153748772572726</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.02221249043941498</v>
+        <v>0.01160344853997231</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.006547905039042234</v>
+        <v>0.006601825356483459</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.01732109859585762</v>
+        <v>0.004552295431494713</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.01712638512253761</v>
+        <v>0.005167381372302771</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.04593328759074211</v>
+        <v>0.009324147365987301</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.003648964688181877</v>
+        <v>5.372101441025734e-05</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.01606986485421658</v>
+        <v>0.004439989570528269</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.006539742927998304</v>
+        <v>0.004119023680686951</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.01260071527212858</v>
+        <v>0.005587041843682528</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.03071312420070171</v>
+        <v>0.0004489024286158383</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.003001312026754022</v>
+        <v>0.006778665818274021</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.02265973575413227</v>
+        <v>0.02081987634301186</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.08591347187757492</v>
+        <v>0.02606723830103874</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.02294287830591202</v>
+        <v>0.003884483128786087</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.02843592502176762</v>
+        <v>0.00155110820196569</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.02732448279857635</v>
+        <v>0.01334845833480358</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.0468871146440506</v>
+        <v>0.0001889442355604842</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.003844337072223425</v>
+        <v>0.002050653798505664</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.01592602021992207</v>
+        <v>0.009276016615331173</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.008421158418059349</v>
+        <v>0.004925076384097338</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.02033368498086929</v>
+        <v>0.002302021021023393</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.02724544145166874</v>
+        <v>0.007376454770565033</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.0558699443936348</v>
+        <v>0.008505343459546566</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.003227668348699808</v>
+        <v>0.0008020452223718166</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.03273732587695122</v>
+        <v>0.002406160812824965</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.009029346518218517</v>
+        <v>0.002849741373211145</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.02252879925072193</v>
+        <v>0.006233676802366972</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.1041633114218712</v>
+        <v>0.01820141822099686</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.002332448493689299</v>
+        <v>0.008200161159038544</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.0553237721323967</v>
+        <v>0.009132233448326588</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.1381904631853104</v>
+        <v>0.01537791080772877</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.07414639741182327</v>
+        <v>0.004820061847567558</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.0347965843975544</v>
+        <v>0.00441083637997508</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.07795548439025879</v>
+        <v>0.001122763962484896</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.08689741790294647</v>
+        <v>0.01759080402553082</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.01709713600575924</v>
+        <v>0.004954868461936712</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.004397479817271233</v>
+        <v>0.009206970222294331</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.01992893405258656</v>
+        <v>0.003823243547230959</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.04665296524763107</v>
+        <v>0.002685058861970901</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.0118165910243988</v>
+        <v>0.00533650116994977</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.008674044162034988</v>
+        <v>0.004750341642647982</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.01754248514771461</v>
+        <v>0.002323062624782324</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.05222496390342712</v>
+        <v>0.002935626776888967</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.00152389844879508</v>
+        <v>0.003648162353783846</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.00925891287624836</v>
+        <v>0.007605982478708029</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.008406385779380798</v>
+        <v>0.001934012863785028</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.01691947877407074</v>
+        <v>0.009140060283243656</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.008496341295540333</v>
+        <v>0.01928723603487015</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.06225697696208954</v>
+        <v>0.0001922515220940113</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.02434246242046356</v>
+        <v>0.004521270282566547</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.003728784853592515</v>
+        <v>0.0005029677413403988</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.03418480232357979</v>
+        <v>0.01004058867692947</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.04730610921978951</v>
+        <v>0.009153512306511402</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.02348101884126663</v>
+        <v>0.003122331574559212</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.01237337663769722</v>
+        <v>0.004412340000271797</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.01227154955267906</v>
+        <v>0.002291495678946376</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.004872404038906097</v>
+        <v>0.002804504241794348</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.03524854406714439</v>
+        <v>0.009713838808238506</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.05464235320687294</v>
+        <v>0.001600896473973989</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.006044489797204733</v>
+        <v>0.005498339887708426</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.01762466877698898</v>
+        <v>0.007543068379163742</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.008061209693551064</v>
+        <v>0.003851872868835926</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.001410686643794179</v>
+        <v>0.005142662674188614</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.002186570316553116</v>
+        <v>0.002641882281750441</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.02149504795670509</v>
+        <v>0.0007941827643662691</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.009077954106032848</v>
+        <v>0.001236007083207369</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.02191021665930748</v>
+        <v>0.002140692202374339</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.03294096887111664</v>
+        <v>0.0118658822029829</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.006756436079740524</v>
+        <v>0.008109920658171177</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.06415755301713943</v>
+        <v>0.009646435268223286</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.009455417282879353</v>
+        <v>0.00932491198182106</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.002300839172676206</v>
+        <v>0.0003787404857575893</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.01533821318298578</v>
+        <v>0.0112902969121933</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.01647528260946274</v>
+        <v>0.006616777740418911</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.01956096850335598</v>
+        <v>0.001674843253567815</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.02531740441918373</v>
+        <v>0.00373462401330471</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.05133505910634995</v>
+        <v>0.007220138795673847</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.007101840805262327</v>
+        <v>0.0007375297718681395</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.03794191032648087</v>
+        <v>0.003894662950187922</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.001663489267230034</v>
+        <v>0.001118423184379935</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.00418736832216382</v>
+        <v>0.002846666146069765</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.03303371369838715</v>
+        <v>0.01017085928469896</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.03248609974980354</v>
+        <v>0.0009778911480680108</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.01462409645318985</v>
+        <v>0.01004955265671015</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.01250561699271202</v>
+        <v>0.002840294037014246</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.03427149727940559</v>
+        <v>0.0109372129663825</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.006289049983024597</v>
+        <v>0.002879859879612923</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.01138883456587791</v>
+        <v>0.01125427894294262</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.0202169194817543</v>
+        <v>0.00450501311570406</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.005741136614233255</v>
+        <v>0.003034868743270636</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.0005496252560988069</v>
+        <v>0.01951811462640762</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.01920489221811295</v>
+        <v>0.02671585604548454</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.02491142973303795</v>
+        <v>0.003558075753971934</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.09443974494934082</v>
+        <v>0.003170373383909464</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.05811580270528793</v>
+        <v>0.01843459904193878</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.02581291645765305</v>
+        <v>0.01446816232055426</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.04642009735107422</v>
+        <v>0.01104537397623062</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.01583456806838512</v>
+        <v>0.01941778883337975</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.01190048269927502</v>
+        <v>0.01333321258425713</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.01130483113229275</v>
+        <v>0.008779123425483704</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.01539077796041965</v>
+        <v>0.002311976160854101</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.007468639872968197</v>
+        <v>0.000477642985060811</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.1376537084579468</v>
+        <v>0.0001526766282040626</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.0239420048892498</v>
+        <v>0.00189726916141808</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.02829000726342201</v>
+        <v>0.0002270344848511741</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.03428639844059944</v>
+        <v>0.0181830171495676</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.0009901318699121475</v>
+        <v>0.005215059034526348</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1.209691617987119e-07</v>
+        <v>1.137858703259553e-06</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0001789727830328047</v>
+        <v>9.674134344095364e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>1.604307908564806e-05</v>
+        <v>4.027783870697021e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>6.431688962038606e-05</v>
+        <v>8.640678970550653e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>7.820432983862702e-06</v>
+        <v>3.288729567429982e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001014630397548899</v>
+        <v>0.0001014059671433643</v>
       </c>
       <c r="G7" t="n">
-        <v>1.517002601758577e-05</v>
+        <v>1.206260208164167e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>3.376680979272351e-05</v>
+        <v>5.089568003313616e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>5.763768058386631e-07</v>
+        <v>4.637069650925696e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>3.719802771229297e-05</v>
+        <v>5.802404302812647e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001480976497987285</v>
+        <v>0.0001229468471137807</v>
       </c>
       <c r="L7" t="n">
-        <v>5.919626346440054e-06</v>
+        <v>5.647699435940012e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>7.273259689100087e-05</v>
+        <v>3.221366205252707e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>3.361355993547477e-06</v>
+        <v>1.783012339728884e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>9.886125917546451e-05</v>
+        <v>0.0001018659022520296</v>
       </c>
       <c r="P7" t="n">
-        <v>3.045614903385285e-06</v>
+        <v>2.938138550234726e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.786333086783998e-06</v>
+        <v>3.565518272807822e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>3.301408924016869e-07</v>
+        <v>7.655590707145166e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>2.412675939922337e-06</v>
+        <v>1.831199483603996e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>2.10292619158281e-05</v>
+        <v>1.210798654938117e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>7.993124199856538e-06</v>
+        <v>7.43202690500766e-07</v>
       </c>
       <c r="V7" t="n">
-        <v>2.621561179694254e-05</v>
+        <v>1.731479642330669e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>1.130786495195935e-05</v>
+        <v>1.091434205591213e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>9.047964340425096e-06</v>
+        <v>3.419533459236845e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.141358764783945e-06</v>
+        <v>9.350391337648034e-06</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.057555684586987e-05</v>
+        <v>1.643002360651735e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.557012627832592e-08</v>
+        <v>2.533262431825278e-06</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.73752305272501e-05</v>
+        <v>1.714736754365731e-06</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.412446337984875e-05</v>
+        <v>7.247803296195343e-06</v>
       </c>
       <c r="AD7" t="n">
-        <v>8.632547178422101e-06</v>
+        <v>1.070267990144202e-05</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.518688713986194e-05</v>
+        <v>2.327206857444253e-05</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.240142410097178e-06</v>
+        <v>2.124536331393756e-05</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.307707836735062e-05</v>
+        <v>2.227441655122675e-05</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.017619888443733e-05</v>
+        <v>6.754909918527119e-06</v>
       </c>
       <c r="AI7" t="n">
-        <v>9.073262845049612e-06</v>
+        <v>4.838926543015987e-05</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.614555230844417e-06</v>
+        <v>1.553315996716265e-05</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.073465839202981e-05</v>
+        <v>7.220241968752816e-06</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.485873963247286e-05</v>
+        <v>2.64822447206825e-05</v>
       </c>
       <c r="AM7" t="n">
-        <v>4.793605967279291e-06</v>
+        <v>3.926088538719341e-07</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.186932033509947e-05</v>
+        <v>1.909367347252555e-05</v>
       </c>
       <c r="AO7" t="n">
-        <v>3.637955160229467e-06</v>
+        <v>8.120716302073561e-06</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.244321487727575e-05</v>
+        <v>8.183537829609122e-06</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.683066693658475e-05</v>
+        <v>2.447307451802772e-06</v>
       </c>
       <c r="AR7" t="n">
-        <v>6.698216566292103e-06</v>
+        <v>2.353278068767395e-05</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.764608714438509e-05</v>
+        <v>1.112805057346122e-05</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.906479883473366e-05</v>
+        <v>1.700706707197241e-05</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.0001123256806749851</v>
+        <v>0.0001243808947037905</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.01658235710056e-06</v>
+        <v>8.091355994110927e-06</v>
       </c>
       <c r="AW7" t="n">
-        <v>9.144869181909598e-06</v>
+        <v>1.998015613935422e-05</v>
       </c>
       <c r="AX7" t="n">
-        <v>3.4481861803215e-05</v>
+        <v>3.160502819810063e-05</v>
       </c>
       <c r="AY7" t="n">
-        <v>6.540706817759201e-05</v>
+        <v>7.013447611825541e-05</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3.529824653014657e-06</v>
+        <v>4.462423021323048e-06</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.804062023642473e-05</v>
+        <v>9.193528057949152e-06</v>
       </c>
       <c r="BB7" t="n">
-        <v>9.167072676063981e-06</v>
+        <v>1.483682990510715e-05</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.594937647401821e-06</v>
+        <v>3.001832737936638e-08</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.089586218469776e-05</v>
+        <v>3.223231760784984e-05</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.358114892966114e-05</v>
+        <v>3.097601438639686e-05</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.214086271123961e-05</v>
+        <v>1.687730105004448e-06</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.639584560412914e-05</v>
+        <v>3.053294494748116e-05</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.664454561658204e-05</v>
+        <v>7.492910299333744e-06</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.901174982776865e-05</v>
+        <v>1.885986785055138e-05</v>
       </c>
       <c r="BJ7" t="n">
-        <v>3.642940282588825e-05</v>
+        <v>1.399073607899481e-05</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.543733666650951e-06</v>
+        <v>2.726615548453992e-06</v>
       </c>
       <c r="BL7" t="n">
-        <v>2.546879386500223e-06</v>
+        <v>6.296218543866416e-06</v>
       </c>
       <c r="BM7" t="n">
-        <v>2.961016980407294e-05</v>
+        <v>1.37147389978054e-05</v>
       </c>
       <c r="BN7" t="n">
-        <v>2.290582415298559e-05</v>
+        <v>5.578778655035421e-06</v>
       </c>
       <c r="BO7" t="n">
-        <v>2.929771653725766e-05</v>
+        <v>6.163979378470685e-06</v>
       </c>
       <c r="BP7" t="n">
-        <v>2.261517920487677e-06</v>
+        <v>2.551954821683466e-06</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.055507815792225e-06</v>
+        <v>5.827356744703138e-06</v>
       </c>
       <c r="BR7" t="n">
-        <v>1.413334939570632e-05</v>
+        <v>6.175810995046049e-06</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.4602368537453e-05</v>
+        <v>1.551167088109651e-06</v>
       </c>
       <c r="BT7" t="n">
-        <v>8.709856956556905e-06</v>
+        <v>9.08020774659235e-06</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.324301229033154e-05</v>
+        <v>2.526704520278145e-06</v>
       </c>
       <c r="BV7" t="n">
-        <v>6.14357486483641e-05</v>
+        <v>6.379223486874253e-05</v>
       </c>
       <c r="BW7" t="n">
-        <v>2.635896089486778e-05</v>
+        <v>7.767148417769931e-07</v>
       </c>
       <c r="BX7" t="n">
-        <v>8.695769793121144e-07</v>
+        <v>2.059577855106909e-05</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.463350236008409e-05</v>
+        <v>1.75397508428432e-05</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.229078381787986e-05</v>
+        <v>5.538633558899164e-05</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.826446001970908e-06</v>
+        <v>1.563870318932459e-05</v>
       </c>
       <c r="CB7" t="n">
-        <v>1.49874667840777e-05</v>
+        <v>1.172968677565223e-05</v>
       </c>
       <c r="CC7" t="n">
-        <v>9.349677384307142e-06</v>
+        <v>4.292781795811607e-06</v>
       </c>
       <c r="CD7" t="n">
-        <v>3.383256171218818e-06</v>
+        <v>2.016205598920351e-06</v>
       </c>
       <c r="CE7" t="n">
-        <v>3.070324237341993e-05</v>
+        <v>3.433008896536194e-05</v>
       </c>
       <c r="CF7" t="n">
-        <v>1.695028731774073e-05</v>
+        <v>7.238900252559688e-06</v>
       </c>
       <c r="CG7" t="n">
-        <v>9.619667252991349e-06</v>
+        <v>6.424710591090843e-06</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.461676492908737e-05</v>
+        <v>8.278318546217633e-07</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.069460358849028e-05</v>
+        <v>2.152455817849841e-05</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.114530277845915e-05</v>
+        <v>8.437447149844957e-07</v>
       </c>
       <c r="CK7" t="n">
-        <v>6.558315362781286e-06</v>
+        <v>8.870434612617828e-06</v>
       </c>
       <c r="CL7" t="n">
-        <v>5.370329290599329e-06</v>
+        <v>3.189032668160507e-06</v>
       </c>
       <c r="CM7" t="n">
-        <v>3.818198456428945e-05</v>
+        <v>1.050163518812042e-05</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.631874849612359e-05</v>
+        <v>3.023603130714037e-05</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.019790147438471e-06</v>
+        <v>2.115086135745514e-05</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.798924106173217e-05</v>
+        <v>3.246676351409405e-05</v>
       </c>
       <c r="CQ7" t="n">
-        <v>5.961157057754463e-06</v>
+        <v>3.078276859014295e-05</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.082300605048658e-05</v>
+        <v>1.943825009220745e-05</v>
       </c>
       <c r="CS7" t="n">
-        <v>1.706709736026824e-05</v>
+        <v>8.137101758620702e-06</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.044155553448945e-05</v>
+        <v>8.556833563488908e-06</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.324942059000023e-05</v>
+        <v>3.453667886788025e-06</v>
       </c>
       <c r="CV7" t="n">
-        <v>3.302275899841334e-06</v>
+        <v>4.243037437845487e-06</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.649153248057701e-05</v>
+        <v>3.129069591523148e-05</v>
       </c>
       <c r="CX7" t="n">
-        <v>2.066791603283491e-05</v>
+        <v>1.234095725521911e-05</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.625964068807662e-05</v>
+        <v>1.213645009556785e-05</v>
       </c>
       <c r="CZ7" t="n">
-        <v>1.563420846650843e-05</v>
+        <v>1.405522652930813e-06</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.388653436151799e-05</v>
+        <v>2.51224082603585e-05</v>
       </c>
       <c r="DB7" t="n">
-        <v>8.124496162054129e-06</v>
+        <v>4.330969659349648e-06</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.15412503873813e-05</v>
+        <v>5.719251021218952e-06</v>
       </c>
       <c r="DD7" t="n">
-        <v>5.268547738523921e-06</v>
+        <v>3.129992762751499e-07</v>
       </c>
       <c r="DE7" t="n">
-        <v>7.149291377572808e-06</v>
+        <v>3.668046247184975e-06</v>
       </c>
       <c r="DF7" t="n">
-        <v>2.834182305377908e-05</v>
+        <v>2.614462755445857e-05</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.231508915429004e-05</v>
+        <v>7.471535809600027e-06</v>
       </c>
       <c r="DH7" t="n">
-        <v>3.73663569916971e-05</v>
+        <v>1.118739510275191e-05</v>
       </c>
       <c r="DI7" t="n">
-        <v>4.482151780393906e-06</v>
+        <v>1.154873280029278e-05</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.092112870537676e-05</v>
+        <v>3.686722629936412e-05</v>
       </c>
       <c r="DK7" t="n">
-        <v>2.171526466554496e-05</v>
+        <v>4.494753738981672e-06</v>
       </c>
       <c r="DL7" t="n">
-        <v>1.985400376725011e-05</v>
+        <v>4.854150392930023e-05</v>
       </c>
       <c r="DM7" t="n">
-        <v>1.141795291914605e-05</v>
+        <v>1.256905306945555e-05</v>
       </c>
       <c r="DN7" t="n">
-        <v>3.346838639117777e-06</v>
+        <v>9.272581337427255e-06</v>
       </c>
       <c r="DO7" t="n">
-        <v>8.129723028105218e-06</v>
+        <v>1.281319600821007e-05</v>
       </c>
       <c r="DP7" t="n">
-        <v>1.038955633703154e-05</v>
+        <v>7.780543455737643e-06</v>
       </c>
       <c r="DQ7" t="n">
-        <v>1.036633511830587e-05</v>
+        <v>5.098125257063657e-06</v>
       </c>
       <c r="DR7" t="n">
-        <v>1.922913543239702e-05</v>
+        <v>1.445074985895189e-06</v>
       </c>
       <c r="DS7" t="n">
-        <v>8.518064532836434e-06</v>
+        <v>1.286361384700285e-05</v>
       </c>
       <c r="DT7" t="n">
-        <v>6.352576747303829e-06</v>
+        <v>9.247572961612605e-06</v>
       </c>
       <c r="DU7" t="n">
-        <v>8.447467735095415e-06</v>
+        <v>2.047214002232067e-05</v>
       </c>
       <c r="DV7" t="n">
-        <v>1.263328886125237e-05</v>
+        <v>5.161254648555769e-06</v>
       </c>
       <c r="DW7" t="n">
-        <v>4.279700988263357e-06</v>
+        <v>2.019456405832898e-05</v>
       </c>
       <c r="DX7" t="n">
-        <v>1.789049201761372e-05</v>
+        <v>2.458538074279204e-05</v>
       </c>
       <c r="DY7" t="n">
-        <v>1.14823078547488e-05</v>
+        <v>1.782115577952936e-05</v>
       </c>
       <c r="DZ7" t="n">
-        <v>5.541766768146772e-06</v>
+        <v>1.934624833666021e-07</v>
       </c>
       <c r="EA7" t="n">
-        <v>4.562990397971589e-06</v>
+        <v>1.939449430210516e-05</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.06262323242845e-05</v>
+        <v>2.648653025971726e-05</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.170127911289455e-06</v>
+        <v>5.203010005061515e-06</v>
       </c>
       <c r="ED7" t="n">
-        <v>2.004503130592639e-06</v>
+        <v>2.236115869891364e-05</v>
       </c>
       <c r="EE7" t="n">
-        <v>4.87139004690107e-08</v>
+        <v>2.057296842394862e-05</v>
       </c>
       <c r="EF7" t="n">
-        <v>6.821016995672835e-06</v>
+        <v>6.043725534254918e-06</v>
       </c>
       <c r="EG7" t="n">
-        <v>2.176917587348726e-05</v>
+        <v>1.195009190269047e-05</v>
       </c>
       <c r="EH7" t="n">
-        <v>1.850696935434826e-05</v>
+        <v>4.662325409299228e-06</v>
       </c>
       <c r="EI7" t="n">
-        <v>3.394000941625563e-06</v>
+        <v>2.640988441271475e-06</v>
       </c>
       <c r="EJ7" t="n">
-        <v>7.732670383120421e-06</v>
+        <v>1.129167594626779e-05</v>
       </c>
       <c r="EK7" t="n">
-        <v>8.849394362187013e-06</v>
+        <v>7.771321179461665e-06</v>
       </c>
       <c r="EL7" t="n">
-        <v>1.676779174886178e-05</v>
+        <v>6.976302302064141e-06</v>
       </c>
       <c r="EM7" t="n">
-        <v>2.14161332223739e-06</v>
+        <v>7.071618711051997e-06</v>
       </c>
       <c r="EN7" t="n">
-        <v>4.794912911165738e-07</v>
+        <v>1.170922132587293e-06</v>
       </c>
       <c r="EO7" t="n">
-        <v>6.803436008340213e-06</v>
+        <v>1.088207773136673e-05</v>
       </c>
       <c r="EP7" t="n">
-        <v>2.257309097331017e-05</v>
+        <v>9.643544217396993e-06</v>
       </c>
       <c r="EQ7" t="n">
-        <v>2.10342896025395e-05</v>
+        <v>2.789882955767098e-06</v>
       </c>
       <c r="ER7" t="n">
-        <v>2.330474671907723e-05</v>
+        <v>1.577515286044218e-05</v>
       </c>
       <c r="ES7" t="n">
-        <v>8.189967047655955e-06</v>
+        <v>1.422409786755452e-05</v>
       </c>
       <c r="ET7" t="n">
-        <v>6.400607048817619e-07</v>
+        <v>1.867545734057785e-06</v>
       </c>
       <c r="EU7" t="n">
-        <v>8.417226126766764e-06</v>
+        <v>5.574163424171275e-07</v>
       </c>
       <c r="EV7" t="n">
-        <v>1.984262416954152e-05</v>
+        <v>7.918112714833114e-06</v>
       </c>
       <c r="EW7" t="n">
-        <v>9.071918611880392e-07</v>
+        <v>2.392409987805877e-05</v>
       </c>
       <c r="EX7" t="n">
-        <v>7.179393833212089e-06</v>
+        <v>1.321090621786425e-06</v>
       </c>
       <c r="EY7" t="n">
-        <v>2.584430330898613e-05</v>
+        <v>3.723052213899791e-05</v>
       </c>
       <c r="EZ7" t="n">
-        <v>1.4092917808739e-05</v>
+        <v>8.855541636876296e-06</v>
       </c>
       <c r="FA7" t="n">
-        <v>1.290237196371891e-05</v>
+        <v>1.00916422525188e-05</v>
       </c>
       <c r="FB7" t="n">
-        <v>1.627873825782444e-05</v>
+        <v>3.347290203237208e-06</v>
       </c>
       <c r="FC7" t="n">
-        <v>1.121785044233548e-05</v>
+        <v>2.595657497295178e-05</v>
       </c>
       <c r="FD7" t="n">
-        <v>1.152363256551325e-05</v>
+        <v>1.894622982945293e-07</v>
       </c>
       <c r="FE7" t="n">
-        <v>5.943409632891417e-06</v>
+        <v>8.891733159543946e-06</v>
       </c>
       <c r="FF7" t="n">
-        <v>1.081131267710589e-05</v>
+        <v>4.874973910773406e-06</v>
       </c>
       <c r="FG7" t="n">
-        <v>8.224395969591569e-06</v>
+        <v>3.950092832383234e-06</v>
       </c>
       <c r="FH7" t="n">
-        <v>1.130435180130007e-06</v>
+        <v>2.254611354146618e-05</v>
       </c>
       <c r="FI7" t="n">
-        <v>7.792600626999047e-06</v>
+        <v>1.071415499609429e-05</v>
       </c>
       <c r="FJ7" t="n">
-        <v>3.644360549515113e-05</v>
+        <v>1.023558070301078e-05</v>
       </c>
       <c r="FK7" t="n">
-        <v>1.558378971822094e-05</v>
+        <v>3.917748017556733e-06</v>
       </c>
       <c r="FL7" t="n">
-        <v>2.087195571220946e-05</v>
+        <v>1.615463042980991e-05</v>
       </c>
       <c r="FM7" t="n">
-        <v>3.332765118102543e-06</v>
+        <v>4.693147729994962e-06</v>
       </c>
       <c r="FN7" t="n">
-        <v>9.813731594476849e-06</v>
+        <v>3.032126369362231e-05</v>
       </c>
       <c r="FO7" t="n">
-        <v>7.194887075456791e-06</v>
+        <v>2.669228524609935e-05</v>
       </c>
       <c r="FP7" t="n">
-        <v>1.440500454918947e-06</v>
+        <v>1.30414910017862e-05</v>
       </c>
       <c r="FQ7" t="n">
-        <v>2.791410770441871e-05</v>
+        <v>2.729711013671476e-05</v>
       </c>
       <c r="FR7" t="n">
-        <v>1.265627270186087e-05</v>
+        <v>2.548244628997054e-05</v>
       </c>
       <c r="FS7" t="n">
-        <v>4.1928327846108e-05</v>
+        <v>1.278317995456746e-06</v>
       </c>
       <c r="FT7" t="n">
-        <v>1.35489954118384e-05</v>
+        <v>1.011956919683143e-05</v>
       </c>
       <c r="FU7" t="n">
-        <v>1.923139461723622e-05</v>
+        <v>1.579010859131813e-05</v>
       </c>
       <c r="FV7" t="n">
-        <v>8.41165820020251e-06</v>
+        <v>2.378017416049261e-05</v>
       </c>
       <c r="FW7" t="n">
-        <v>8.090148639894323e-07</v>
+        <v>2.566395232861396e-05</v>
       </c>
       <c r="FX7" t="n">
-        <v>1.157015140051953e-05</v>
+        <v>2.362502709729597e-05</v>
       </c>
       <c r="FY7" t="n">
-        <v>3.580914926715195e-05</v>
+        <v>1.20873828564072e-05</v>
       </c>
       <c r="FZ7" t="n">
-        <v>7.557141088909702e-06</v>
+        <v>5.006713308830513e-06</v>
       </c>
       <c r="GA7" t="n">
-        <v>1.070367397915106e-05</v>
+        <v>2.917814344982617e-05</v>
       </c>
       <c r="GB7" t="n">
-        <v>5.612515906250337e-06</v>
+        <v>2.355172910029069e-06</v>
       </c>
       <c r="GC7" t="n">
-        <v>2.613433707665536e-06</v>
+        <v>3.666667907964438e-05</v>
       </c>
       <c r="GD7" t="n">
-        <v>1.95600550796371e-05</v>
+        <v>2.086762651742902e-05</v>
       </c>
       <c r="GE7" t="n">
-        <v>6.417436816263944e-05</v>
+        <v>8.90859701030422e-06</v>
       </c>
       <c r="GF7" t="n">
-        <v>4.092693416168913e-06</v>
+        <v>5.504695309355156e-06</v>
       </c>
       <c r="GG7" t="n">
-        <v>8.953627911978401e-06</v>
+        <v>6.823315743531566e-06</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.0001386082731187344</v>
+        <v>0.004014092963188887</v>
       </c>
       <c r="B8" t="n">
-        <v>0.003720554290339351</v>
+        <v>0.04411591216921806</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0002309995034011081</v>
+        <v>0.02495519816875458</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001910562277771533</v>
+        <v>0.01020452007651329</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002091638743877411</v>
+        <v>0.005621539428830147</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001418681349605322</v>
+        <v>0.02099454030394554</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0005357424379326403</v>
+        <v>0.0001570750027894974</v>
       </c>
       <c r="H8" t="n">
-        <v>6.476366252172738e-05</v>
+        <v>0.003344167256727815</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0003152618883177638</v>
+        <v>0.01553444750607014</v>
       </c>
       <c r="J8" t="n">
-        <v>0.000109918080852367</v>
+        <v>0.0003931256360374391</v>
       </c>
       <c r="K8" t="n">
-        <v>0.003178672399371862</v>
+        <v>0.04552195221185684</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0002937218232546002</v>
+        <v>0.02971511892974377</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0003805970191024244</v>
+        <v>0.01864480040967464</v>
       </c>
       <c r="N8" t="n">
-        <v>0.001271143322810531</v>
+        <v>0.0001720551081234589</v>
       </c>
       <c r="O8" t="n">
-        <v>0.000816843647044152</v>
+        <v>0.01085358299314976</v>
       </c>
       <c r="P8" t="n">
-        <v>0.00095962273189798</v>
+        <v>0.002250341698527336</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0007132311584427953</v>
+        <v>0.0121593251824379</v>
       </c>
       <c r="R8" t="n">
-        <v>4.631874617189169e-05</v>
+        <v>0.009309234097599983</v>
       </c>
       <c r="S8" t="n">
-        <v>8.482608973281458e-05</v>
+        <v>0.002919060876592994</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0001819163735490292</v>
+        <v>0.006532575003802776</v>
       </c>
       <c r="U8" t="n">
-        <v>2.885804860852659e-05</v>
+        <v>0.01314151752740145</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0006039673462510109</v>
+        <v>0.001406712108291686</v>
       </c>
       <c r="W8" t="n">
-        <v>3.253028626204468e-05</v>
+        <v>0.001145096146501601</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0002733087749220431</v>
+        <v>0.01358054205775261</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0004428486863616854</v>
+        <v>0.001383217866532505</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0001901411305880174</v>
+        <v>0.0002051360788755119</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0005474661593325436</v>
+        <v>0.00790389534085989</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.979400783777237e-05</v>
+        <v>0.00689777871593833</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.224543615942821e-05</v>
+        <v>0.009015647694468498</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.0004701527068391442</v>
+        <v>0.001204090192914009</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.0007679859991185367</v>
+        <v>0.01673748344182968</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0003877205890603364</v>
+        <v>0.01551895774900913</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0003795515222009271</v>
+        <v>0.003414034377783537</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.288471634732559e-05</v>
+        <v>0.008141430094838142</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.0006001172005198896</v>
+        <v>0.00344438711181283</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.000404618593165651</v>
+        <v>0.005795245058834553</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.0001821512851165608</v>
+        <v>0.001078937901183963</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.0006157727912068367</v>
+        <v>0.009659081697463989</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.000238530890783295</v>
+        <v>0.009231844916939735</v>
       </c>
       <c r="AN8" t="n">
-        <v>9.996353037422523e-05</v>
+        <v>0.007446779403835535</v>
       </c>
       <c r="AO8" t="n">
-        <v>3.672441744129173e-05</v>
+        <v>0.01757039502263069</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0004340341547504067</v>
+        <v>0.00851159356534481</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.0001194404612760991</v>
+        <v>0.004749291110783815</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.000342138868290931</v>
+        <v>0.001098435954190791</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.0003383731527719647</v>
+        <v>0.0008886970463208854</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.0005038776434957981</v>
+        <v>0.001575538888573647</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.001884965924546123</v>
+        <v>0.0345587320625782</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.97952356049791e-05</v>
+        <v>0.003666400443762541</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.001807984081096947</v>
+        <v>0.01298380363732576</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.001456532976590097</v>
+        <v>0.001663043280132115</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.0008184247999452055</v>
+        <v>0.007826809771358967</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.0006901276065036654</v>
+        <v>0.0009301831014454365</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.0002868784358724952</v>
+        <v>0.003742025699466467</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.0007321796729229391</v>
+        <v>0.005077917594462633</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.0004185512661933899</v>
+        <v>0.006591788958758116</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.0005756508908234537</v>
+        <v>0.005118462257087231</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.0005289760301820934</v>
+        <v>0.01291711535304785</v>
       </c>
       <c r="BF8" t="n">
-        <v>6.259151268750429e-05</v>
+        <v>0.007264007814228535</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.001166684320196509</v>
+        <v>0.004636500030755997</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.000474061060231179</v>
+        <v>0.01684600673615932</v>
       </c>
       <c r="BI8" t="n">
-        <v>8.709060784894973e-05</v>
+        <v>0.003068801481276751</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.000787838245742023</v>
+        <v>0.003363695926964283</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.0003273831389378756</v>
+        <v>0.009455903433263302</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0001437092723790556</v>
+        <v>0.003289763350039721</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.0003787893801927567</v>
+        <v>0.006940980441868305</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.0002608980285003781</v>
+        <v>0.006021793931722641</v>
       </c>
       <c r="BO8" t="n">
-        <v>6.808697071392089e-05</v>
+        <v>0.01019216887652874</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0009475864935666323</v>
+        <v>0.002235951367765665</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.0002088538749376312</v>
+        <v>0.0003842037112917751</v>
       </c>
       <c r="BR8" t="n">
-        <v>5.747249451815151e-05</v>
+        <v>0.003743584267795086</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.0005717500462196767</v>
+        <v>0.003216065466403961</v>
       </c>
       <c r="BT8" t="n">
-        <v>6.271926395129412e-05</v>
+        <v>0.002991406247019768</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.0004669974441640079</v>
+        <v>0.003130587516352534</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.001307661063037813</v>
+        <v>0.02221422456204891</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.043092045933008e-05</v>
+        <v>0.0016853844281286</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.0006796065717935562</v>
+        <v>0.006488843820989132</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.0006320350803434849</v>
+        <v>0.003204561537131667</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.000173745458596386</v>
+        <v>0.01561240013688803</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.0003769708564504981</v>
+        <v>0.0004024067893624306</v>
       </c>
       <c r="CB8" t="n">
-        <v>9.052166569745168e-05</v>
+        <v>0.001450990908779204</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.0005026119761168957</v>
+        <v>0.009099963121116161</v>
       </c>
       <c r="CD8" t="n">
-        <v>9.601779311196879e-05</v>
+        <v>0.0008671333780512214</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.0003913495747838169</v>
+        <v>0.01480087824165821</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.0001933717867359519</v>
+        <v>0.01064473111182451</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.0003910056839231402</v>
+        <v>0.005818618461489677</v>
       </c>
       <c r="CH8" t="n">
-        <v>4.445565718924627e-05</v>
+        <v>0.0004215155786368996</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.0002261541085317731</v>
+        <v>0.001025581383146346</v>
       </c>
       <c r="CJ8" t="n">
-        <v>5.47540548723191e-06</v>
+        <v>0.0002267765230499208</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.0001196681478177197</v>
+        <v>0.0008627648930996656</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.000410142878536135</v>
+        <v>0.00406725937500596</v>
       </c>
       <c r="CM8" t="n">
-        <v>3.042619391635526e-05</v>
+        <v>0.004509192425757647</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.0005067542078904808</v>
+        <v>0.01232200488448143</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.0001670529745751992</v>
+        <v>0.004699671640992165</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.0007833045674487948</v>
+        <v>0.01428071968257427</v>
       </c>
       <c r="CQ8" t="n">
-        <v>7.724772149231285e-05</v>
+        <v>0.005509800277650356</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.000823642301838845</v>
+        <v>0.013042276725173</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.001030551851727068</v>
+        <v>0.00324687035754323</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.0004742545424960554</v>
+        <v>0.001078549074009061</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.0001690234494162723</v>
+        <v>0.006328847259283066</v>
       </c>
       <c r="CV8" t="n">
-        <v>7.321206794586033e-06</v>
+        <v>0.001318287802860141</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.0004843796486966312</v>
+        <v>0.01503897644579411</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.0002490436600055546</v>
+        <v>0.01117153000086546</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.0005489119794219732</v>
+        <v>0.005293709225952625</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.0001476260367780924</v>
+        <v>0.001249375403858721</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.0003798906109295785</v>
+        <v>0.0004529768484644592</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.0001232583599630743</v>
+        <v>0.0007851053960621357</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.0001874707377282903</v>
+        <v>0.0002869685995392501</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.0003605942474678159</v>
+        <v>0.005450570024549961</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.000144805817399174</v>
+        <v>0.007252853363752365</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.000696835748385638</v>
+        <v>0.02394966222345829</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.0004336155543569475</v>
+        <v>0.0178841594606638</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.002453195163980126</v>
+        <v>0.0113193616271019</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.001740113599225879</v>
+        <v>0.005543442908674479</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.0001377367880195379</v>
+        <v>0.0005026478320360184</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.0009296572534367442</v>
+        <v>0.003613083390519023</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.001216516364365816</v>
+        <v>0.009619760327041149</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.0002158032439183444</v>
+        <v>0.009011249989271164</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.000399493204895407</v>
+        <v>0.00151461863424629</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.0003582770295906812</v>
+        <v>0.003955114632844925</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.0008899194654077291</v>
+        <v>0.005586727522313595</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.0002176416455768049</v>
+        <v>0.001932383631356061</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.0002054366923402995</v>
+        <v>0.004414593800902367</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.0002903505810536444</v>
+        <v>0.008348152041435242</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.0001815177965909243</v>
+        <v>0.0005074178334325552</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.0003016275004483759</v>
+        <v>0.0008806306286714971</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.0004862102796323597</v>
+        <v>0.009670184925198555</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.0002096005191560835</v>
+        <v>0.002804675372317433</v>
       </c>
       <c r="DX8" t="n">
-        <v>5.055231304140761e-05</v>
+        <v>0.007845936343073845</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.0007111962768249214</v>
+        <v>0.008995477110147476</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.0003930603561457247</v>
+        <v>0.005827607121318579</v>
       </c>
       <c r="EA8" t="n">
-        <v>2.887215850932989e-05</v>
+        <v>0.01210261601954699</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.0003014734829775989</v>
+        <v>0.006995291449129581</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.0001453524164389819</v>
+        <v>0.0004255937528796494</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.0003838241682387888</v>
+        <v>0.006541196256875992</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.0002965763560496271</v>
+        <v>0.006091243121773005</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.0003786436282098293</v>
+        <v>0.001114130485802889</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.0003025117330253124</v>
+        <v>0.0147183071821928</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.0004120517696719617</v>
+        <v>0.007153189741075039</v>
       </c>
       <c r="EI8" t="n">
-        <v>3.342660784255713e-05</v>
+        <v>0.004773413762450218</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.0005677255103364587</v>
+        <v>0.0009225588291883469</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.0004729558131657541</v>
+        <v>0.009073968045413494</v>
       </c>
       <c r="EL8" t="n">
-        <v>7.856142474338412e-07</v>
+        <v>0.001027551828883588</v>
       </c>
       <c r="EM8" t="n">
-        <v>3.004140489792917e-05</v>
+        <v>0.0002777947811409831</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.0001675477833487093</v>
+        <v>0.00512088555842638</v>
       </c>
       <c r="EO8" t="n">
-        <v>7.024961814749986e-05</v>
+        <v>0.001111639547161758</v>
       </c>
       <c r="EP8" t="n">
-        <v>6.339618266792968e-05</v>
+        <v>0.001339969225227833</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.0002432503242744133</v>
+        <v>0.005271150730550289</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.0002790083235595375</v>
+        <v>0.0007062489166855812</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.0001859673939179629</v>
+        <v>0.0006017136620357633</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.0006140758050605655</v>
+        <v>0.0007789266528561711</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.000254749960731715</v>
+        <v>0.004052897449582815</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.0003856272669509053</v>
+        <v>0.002428412903100252</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.0001777495635906234</v>
+        <v>0.006315167527645826</v>
       </c>
       <c r="EX8" t="n">
-        <v>3.200824357918464e-05</v>
+        <v>0.001712424331344664</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.0004525848489720374</v>
+        <v>0.01587715931236744</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.0001021881762426347</v>
+        <v>0.009359433315694332</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.0004439156327862293</v>
+        <v>0.007162559777498245</v>
       </c>
       <c r="FB8" t="n">
-        <v>5.017410512664355e-05</v>
+        <v>0.00228992011398077</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.0002409787412034348</v>
+        <v>0.001861372147686779</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.0001017020986182615</v>
+        <v>0.0003561361227184534</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.0001114988554036245</v>
+        <v>0.0009039599681273103</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.0004430067201610655</v>
+        <v>0.005031879525631666</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.0001061541188391857</v>
+        <v>0.0003936843713745475</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.0004920618957839906</v>
+        <v>0.01341167278587818</v>
       </c>
       <c r="FI8" t="n">
-        <v>5.060968760517426e-05</v>
+        <v>0.0007131223101168871</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.0005876041250303388</v>
+        <v>0.004660785663872957</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.0003364443255122751</v>
+        <v>0.01097938977181911</v>
       </c>
       <c r="FL8" t="n">
-        <v>8.736518793739378e-05</v>
+        <v>0.004385783802717924</v>
       </c>
       <c r="FM8" t="n">
-        <v>9.467679774388671e-06</v>
+        <v>0.001934843370690942</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.00047828140668571</v>
+        <v>0.002464205026626587</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.0001295647380175069</v>
+        <v>0.01076971739530563</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.0001132145771407522</v>
+        <v>0.0006028632633388042</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.0007463008514605463</v>
+        <v>0.01439511403441429</v>
       </c>
       <c r="FR8" t="n">
-        <v>3.508048393996432e-05</v>
+        <v>0.01391248032450676</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.0008675287826918066</v>
+        <v>0.01573267951607704</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.000772991101257503</v>
+        <v>0.001922940602526069</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.0002768593840301037</v>
+        <v>0.01151948980987072</v>
       </c>
       <c r="FV8" t="n">
-        <v>0.0001991205936064944</v>
+        <v>0.002261087065562606</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.0001147357688751072</v>
+        <v>0.001504719955846667</v>
       </c>
       <c r="FX8" t="n">
-        <v>4.581687971949577e-05</v>
+        <v>0.001164231449365616</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.0001935619511641562</v>
+        <v>0.0116525162011385</v>
       </c>
       <c r="FZ8" t="n">
-        <v>5.071511623100378e-06</v>
+        <v>0.01854153908789158</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.0002117580734193325</v>
+        <v>0.02488045953214169</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.0007534403121098876</v>
+        <v>0.004683493636548519</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.0008082689018920064</v>
+        <v>0.003013588488101959</v>
       </c>
       <c r="GD8" t="n">
-        <v>7.96788590378128e-05</v>
+        <v>0.0070311538875103</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.001118556247092783</v>
+        <v>0.008759923279285431</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.000189085621968843</v>
+        <v>0.004274340812116861</v>
       </c>
       <c r="GG8" t="n">
-        <v>5.462991612148471e-05</v>
+        <v>0.002515934407711029</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.01861057803034782</v>
+        <v>7.691685459576547e-05</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2371256947517395</v>
+        <v>0.0003072718100156635</v>
       </c>
       <c r="C9" t="n">
-        <v>0.006445686332881451</v>
+        <v>8.086328307399526e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1187348589301109</v>
+        <v>0.000139282681629993</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0323340892791748</v>
+        <v>2.964583836728707e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>0.203238770365715</v>
+        <v>0.0002460949181113392</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001469207927584648</v>
+        <v>7.335331611102447e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.08297643065452576</v>
+        <v>5.382629024097696e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01685802266001701</v>
+        <v>2.620859049784485e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.04856201261281967</v>
+        <v>6.06481044087559e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2230824679136276</v>
+        <v>0.0003722988767549396</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004515244159847498</v>
+        <v>3.619294875534251e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>0.08597143739461899</v>
+        <v>0.0002394993061898276</v>
       </c>
       <c r="N9" t="n">
-        <v>0.003100891131907701</v>
+        <v>0.0001041201467160136</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1893228590488434</v>
+        <v>0.0003065447090193629</v>
       </c>
       <c r="P9" t="n">
-        <v>0.01312901824712753</v>
+        <v>1.62144388013985e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03677046671509743</v>
+        <v>5.395979678723961e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>0.005585072096437216</v>
+        <v>5.801376391900703e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01078718341886997</v>
+        <v>2.669899913598783e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01615801453590393</v>
+        <v>3.404895687708631e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>0.02153419330716133</v>
+        <v>3.690987796289846e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03197560459375381</v>
+        <v>3.376134191057645e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0583316832780838</v>
+        <v>1.433596480637789e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0186696108430624</v>
+        <v>4.896780956187285e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.01893303729593754</v>
+        <v>3.684147304738872e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.05739665031433105</v>
+        <v>0.0001411184493917972</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03486910462379456</v>
+        <v>8.815244655124843e-06</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.001438789069652557</v>
+        <v>6.378634134307504e-05</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.0133759044110775</v>
+        <v>3.182239743182436e-05</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.009325931780040264</v>
+        <v>2.891817348427139e-05</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.009861024096608162</v>
+        <v>7.368098886217922e-05</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.01389772724360228</v>
+        <v>7.501863001380116e-05</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0143308974802494</v>
+        <v>9.57558659138158e-05</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.01284622400999069</v>
+        <v>1.038577920553507e-05</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.008509773761034012</v>
+        <v>0.0002094470110023394</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.0130384424701333</v>
+        <v>3.103895505773835e-05</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.02094356715679169</v>
+        <v>7.265630119945854e-05</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.04187099635601044</v>
+        <v>3.806336462730542e-05</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.002297541126608849</v>
+        <v>3.82097132387571e-05</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.008399352431297302</v>
+        <v>3.109603494522162e-05</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.0009102043695747852</v>
+        <v>3.698737600643653e-06</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.02807123400270939</v>
+        <v>4.573251771944342e-06</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.00256158341653645</v>
+        <v>3.918401489499956e-05</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.01317024976015091</v>
+        <v>0.000139212075737305</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.02483553253114223</v>
+        <v>2.128598316630814e-05</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.03235190361738205</v>
+        <v>0.0001164827408501878</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.1736998409032822</v>
+        <v>0.0002425203565508127</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.005375235341489315</v>
+        <v>6.464351463364437e-05</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.04496053233742714</v>
+        <v>6.902298628119752e-05</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.01709465309977531</v>
+        <v>0.0001876322639873251</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.1077655255794525</v>
+        <v>0.0001726334303384647</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.02394679933786392</v>
+        <v>5.942084499110933e-06</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.0204777829349041</v>
+        <v>8.392642484977841e-06</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.06129929423332214</v>
+        <v>4.703050944954157e-05</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.0216589942574501</v>
+        <v>1.221837555931415e-05</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.03791249915957451</v>
+        <v>5.933384090894833e-05</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.04754414781928062</v>
+        <v>1.650933700148016e-05</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.00249142711982131</v>
+        <v>0.0001169502138509415</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.03823554515838623</v>
+        <v>7.435803854605183e-05</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.06128839775919914</v>
+        <v>5.427400537882932e-05</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.01917595602571964</v>
+        <v>2.736876922426745e-05</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.01999368704855442</v>
+        <v>8.326924580615014e-05</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.01394461281597614</v>
+        <v>5.294046422932297e-05</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.0001503666862845421</v>
+        <v>1.321857234870549e-05</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.0546487532556057</v>
+        <v>3.645935066742823e-05</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.00672224722802639</v>
+        <v>1.886590212052397e-06</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.01508929952979088</v>
+        <v>6.962921179365367e-05</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.003939978778362274</v>
+        <v>2.317588041478302e-05</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.001912229578010738</v>
+        <v>1.05286089819856e-05</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.01697306707501411</v>
+        <v>0.000124360216432251</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.006471746601164341</v>
+        <v>1.833459464251064e-05</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.006727925501763821</v>
+        <v>8.065887232078239e-05</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.01539248321205378</v>
+        <v>3.784135333262384e-05</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.09007550776004791</v>
+        <v>0.0001345257624052465</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.01483060978353024</v>
+        <v>2.049492104561068e-05</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.03765137121081352</v>
+        <v>6.383928848663345e-05</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.02255133725702763</v>
+        <v>3.248325811000541e-06</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.04176545515656471</v>
+        <v>8.927455201046541e-05</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.01393814291805029</v>
+        <v>3.400472633074969e-05</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.0002313493750989437</v>
+        <v>2.527182368794456e-05</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.04003608599305153</v>
+        <v>4.524458199739456e-05</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.001381583511829376</v>
+        <v>1.066539516614284e-05</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.03101350367069244</v>
+        <v>9.209743438987061e-05</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.02275220118463039</v>
+        <v>3.784714863286354e-06</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.01631583645939827</v>
+        <v>3.520170139381662e-05</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.005913358181715012</v>
+        <v>1.502861596236471e-05</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.0315823070704937</v>
+        <v>8.074149081949145e-05</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.01641953736543655</v>
+        <v>2.530566962377634e-05</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.01131806336343288</v>
+        <v>1.880705167423002e-05</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.02083336561918259</v>
+        <v>3.772290074266493e-05</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.05034342035651207</v>
+        <v>3.250980807933956e-05</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.007730855606496334</v>
+        <v>9.80980257736519e-05</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.005318635143339634</v>
+        <v>8.703589264769107e-05</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.0362873338162899</v>
+        <v>0.0001225228043040261</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.001192907337099314</v>
+        <v>2.261467670905404e-06</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.006107674911618233</v>
+        <v>8.500288822688162e-05</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.04923717677593231</v>
+        <v>5.848703949595802e-06</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.04619910195469856</v>
+        <v>0.0001025323872454464</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.009500612504780293</v>
+        <v>3.769935574382544e-05</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.0001195187214761972</v>
+        <v>2.348103953409009e-05</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.02730012498795986</v>
+        <v>8.889888704288751e-05</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.01881650649011135</v>
+        <v>1.058936959452694e-06</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.02870979718863964</v>
+        <v>5.380349466577172e-05</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.007997095584869385</v>
+        <v>1.63135991897434e-05</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.03324554488062859</v>
+        <v>8.741121564526111e-05</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.01652374491095543</v>
+        <v>5.449879608931951e-06</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.02352634444832802</v>
+        <v>2.382257298449986e-05</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.01090287044644356</v>
+        <v>3.269608714617789e-05</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.005340783856809139</v>
+        <v>2.506393684598152e-05</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.01120668277144432</v>
+        <v>5.012480323784985e-05</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.007310524582862854</v>
+        <v>4.254374653100967e-05</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.08527781814336777</v>
+        <v>1.193059233628446e-05</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.04483778774738312</v>
+        <v>0.0001924586395034567</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.02795918844640255</v>
+        <v>8.084376895567402e-05</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.004713171161711216</v>
+        <v>5.913638233323582e-05</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.03878370299935341</v>
+        <v>1.742140739224851e-06</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.02164205349981785</v>
+        <v>2.927568857558072e-06</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.004920377396047115</v>
+        <v>3.202759035048075e-05</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.0031406763009727</v>
+        <v>6.178076728247106e-05</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.01693795807659626</v>
+        <v>1.819178214645945e-05</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.0004337313584983349</v>
+        <v>5.311001586960629e-05</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.008421801961958408</v>
+        <v>2.330850657017436e-05</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.002283880952745676</v>
+        <v>2.551390934968367e-05</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.00104664801619947</v>
+        <v>5.983177834423259e-05</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.002834649290889502</v>
+        <v>0.0001228998880833387</v>
       </c>
       <c r="DV9" t="n">
-        <v>0.02057269774377346</v>
+        <v>4.802750481758267e-05</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.0001513669267296791</v>
+        <v>3.133450445602648e-05</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.0252188928425312</v>
+        <v>1.87354235094972e-05</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.01928079500794411</v>
+        <v>3.274233677075244e-05</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.008103316649794579</v>
+        <v>4.372009425424039e-05</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.00138934375718236</v>
+        <v>6.830459460616112e-05</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.01551226247102022</v>
+        <v>4.313945100875571e-05</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.0007104217074811459</v>
+        <v>3.700749584822915e-05</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.004836912266910076</v>
+        <v>6.078441219870001e-05</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.0101972296833992</v>
+        <v>7.395865395665169e-05</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.01348243094980717</v>
+        <v>2.134999022018746e-06</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.03572700917720795</v>
+        <v>2.157592825824395e-05</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.01130735781043768</v>
+        <v>3.755558282136917e-05</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.007187223993241787</v>
+        <v>1.986643837881275e-06</v>
       </c>
       <c r="EJ9" t="n">
-        <v>8.202483877539635e-05</v>
+        <v>1.140911626862362e-05</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.02313658222556114</v>
+        <v>2.899988248827867e-05</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.01592731103301048</v>
+        <v>1.62789237947436e-05</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.006859187036752701</v>
+        <v>6.775162091798848e-06</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.01097701955586672</v>
+        <v>1.743659959174693e-05</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.001153502613306046</v>
+        <v>3.267017018515617e-05</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.01492869574576616</v>
+        <v>4.102702951058745e-05</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.01754457503557205</v>
+        <v>4.007309325970709e-05</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.02199815027415752</v>
+        <v>4.721219738712534e-05</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.01740813255310059</v>
+        <v>4.862611240241677e-05</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.02959133125841618</v>
+        <v>6.817911344114691e-05</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.03905221074819565</v>
+        <v>2.747707912931219e-05</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.06678984314203262</v>
+        <v>4.716587864095345e-05</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.005901198834180832</v>
+        <v>4.893737786915153e-05</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.004123020451515913</v>
+        <v>2.409339685982559e-05</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.02567833662033081</v>
+        <v>0.0001116581843234599</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0.0155309671536088</v>
+        <v>1.008548451864044e-06</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.02027012594044209</v>
+        <v>6.7401364503894e-05</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.004942032974213362</v>
+        <v>3.361576091265306e-05</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.02759478241205215</v>
+        <v>6.965905777178705e-05</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.02859637886285782</v>
+        <v>1.932503073476255e-05</v>
       </c>
       <c r="FE9" t="n">
-        <v>0.01527217030525208</v>
+        <v>2.0131274141022e-05</v>
       </c>
       <c r="FF9" t="n">
-        <v>0.02188032492995262</v>
+        <v>1.615869223314803e-05</v>
       </c>
       <c r="FG9" t="n">
-        <v>0.01078008860349655</v>
+        <v>2.069177753583062e-05</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.007210119161754847</v>
+        <v>0.0001290930085815489</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.01567903906106949</v>
+        <v>7.44444114388898e-05</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.03749755769968033</v>
+        <v>9.857016993919387e-05</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.008984709158539772</v>
+        <v>4.490958963287994e-05</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.01825453341007233</v>
+        <v>0.0001205470762215555</v>
       </c>
       <c r="FM9" t="n">
-        <v>0.0005547641776502132</v>
+        <v>1.38623763632495e-05</v>
       </c>
       <c r="FN9" t="n">
-        <v>0.01815658807754517</v>
+        <v>7.851590635254979e-05</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.01698459312319756</v>
+        <v>6.700785888824612e-05</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.01559801958501339</v>
+        <v>1.580220487085171e-05</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.03934814780950546</v>
+        <v>3.913992986781523e-05</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.03251191973686218</v>
+        <v>0.0001950183359440416</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.0003659832291305065</v>
+        <v>3.248353459639475e-05</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.004876871593296528</v>
+        <v>0.0001110694793169387</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.01117378659546375</v>
+        <v>1.0976964404108e-05</v>
       </c>
       <c r="FV9" t="n">
-        <v>0.02655639685690403</v>
+        <v>3.012898014276288e-05</v>
       </c>
       <c r="FW9" t="n">
-        <v>0.004022484645247459</v>
+        <v>2.379688339715358e-05</v>
       </c>
       <c r="FX9" t="n">
-        <v>0.01491651218384504</v>
+        <v>1.347186116618104e-05</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.04654818028211594</v>
+        <v>1.862807766883634e-05</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.01586588658392429</v>
+        <v>6.941500760149211e-05</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.02829737588763237</v>
+        <v>6.398886034730822e-05</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.01245159562677145</v>
+        <v>1.255087590834592e-05</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.01304948329925537</v>
+        <v>0.0001825021317927167</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.01801168918609619</v>
+        <v>8.525674638804048e-05</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.1004845723509789</v>
+        <v>2.506627606635448e-05</v>
       </c>
       <c r="GF9" t="n">
-        <v>0.001938051544129848</v>
+        <v>3.56614327756688e-05</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.004058975260704756</v>
+        <v>2.736289025051519e-05</v>
       </c>
     </row>
     <row r="10">
@@ -6689,1140 +6689,1140 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.000144314777571708</v>
+        <v>9.684785027275211e-07</v>
       </c>
       <c r="B12" t="n">
-        <v>0.001869396190159023</v>
+        <v>5.619906914944295e-06</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0001237125543411821</v>
+        <v>4.913781594950706e-07</v>
       </c>
       <c r="D12" t="n">
-        <v>0.000392859656130895</v>
+        <v>1.713130131975049e-06</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0004673385119531304</v>
+        <v>2.78321499536105e-06</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0004175872600171715</v>
+        <v>8.052302291616797e-06</v>
       </c>
       <c r="G12" t="n">
-        <v>0.000289405114017427</v>
+        <v>2.796407898131292e-06</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0002337529003852978</v>
+        <v>5.58515966986306e-06</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0002795870532281697</v>
+        <v>5.080403298052261e-07</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0002041987463599071</v>
+        <v>5.367971880332334e-07</v>
       </c>
       <c r="K12" t="n">
-        <v>0.001648076227866113</v>
+        <v>6.849195415270515e-06</v>
       </c>
       <c r="L12" t="n">
-        <v>4.456980605027638e-06</v>
+        <v>2.680597390281036e-06</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0002343781525269151</v>
+        <v>4.080195594724501e-06</v>
       </c>
       <c r="N12" t="n">
-        <v>7.928599370643497e-05</v>
+        <v>6.673756161035271e-06</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0003300730313640088</v>
+        <v>1.065810465661343e-05</v>
       </c>
       <c r="P12" t="n">
-        <v>0.0001585933787282556</v>
+        <v>1.781623495844542e-06</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0001919291680678725</v>
+        <v>3.687071966851363e-06</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0003656261833384633</v>
+        <v>1.2646103186853e-07</v>
       </c>
       <c r="S12" t="n">
-        <v>8.659066224936396e-05</v>
+        <v>1.97168361637523e-08</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0002210674429079518</v>
+        <v>4.724053042082232e-07</v>
       </c>
       <c r="U12" t="n">
-        <v>6.789417966501787e-05</v>
+        <v>1.110426183004165e-06</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0001651412167120725</v>
+        <v>6.557239657922764e-07</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0002051943447440863</v>
+        <v>9.018548894346168e-07</v>
       </c>
       <c r="X12" t="n">
-        <v>6.040728112566285e-05</v>
+        <v>1.340832113783108e-06</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.820397821778897e-05</v>
+        <v>8.903189154807478e-07</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.0003487916255835444</v>
+        <v>2.789565314742504e-06</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.0001241104037035257</v>
+        <v>7.29408384358976e-07</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.000136229646159336</v>
+        <v>1.666501248109853e-06</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.0001441746426280588</v>
+        <v>1.679826482359204e-07</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.813095877878368e-05</v>
+        <v>1.801201676698838e-07</v>
       </c>
       <c r="AE12" t="n">
-        <v>9.937054710462689e-05</v>
+        <v>2.139785920007853e-06</v>
       </c>
       <c r="AF12" t="n">
-        <v>6.070603194530122e-05</v>
+        <v>1.874179702099354e-06</v>
       </c>
       <c r="AG12" t="n">
-        <v>5.553246955969371e-05</v>
+        <v>1.961207090062089e-06</v>
       </c>
       <c r="AH12" t="n">
-        <v>5.011488974560052e-05</v>
+        <v>3.803770027843711e-07</v>
       </c>
       <c r="AI12" t="n">
-        <v>6.951438263058662e-05</v>
+        <v>4.753524990519509e-06</v>
       </c>
       <c r="AJ12" t="n">
-        <v>4.024465306429192e-05</v>
+        <v>1.498428218837944e-06</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.0003018919960595667</v>
+        <v>7.092679084053088e-07</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.0001816431031329557</v>
+        <v>1.90117475540319e-07</v>
       </c>
       <c r="AM12" t="n">
-        <v>3.401021604076959e-05</v>
+        <v>1.454897073926986e-07</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.0001500809448771179</v>
+        <v>3.587396406601329e-07</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.0001624881697352976</v>
+        <v>1.036801222653594e-06</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.00012848453479819</v>
+        <v>6.078618071114761e-07</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.0001283932651858777</v>
+        <v>2.119687110280211e-07</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.588609666214325e-05</v>
+        <v>2.395747287664562e-06</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.0001367280056001619</v>
+        <v>3.810362727563188e-07</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.662845119833946e-05</v>
+        <v>1.187052134810074e-06</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.001121829729527235</v>
+        <v>7.045618986012414e-06</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.0001618846436031163</v>
+        <v>9.731909358379198e-07</v>
       </c>
       <c r="AW12" t="n">
-        <v>8.812497981125489e-05</v>
+        <v>9.906088962452486e-07</v>
       </c>
       <c r="AX12" t="n">
-        <v>7.229076436487958e-05</v>
+        <v>3.979099801654229e-06</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.0001172524498542771</v>
+        <v>6.843269147793762e-06</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.0004197589005343616</v>
+        <v>4.955153372065979e-07</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.0001679434790275991</v>
+        <v>2.002920837185229e-06</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.0001625605946173891</v>
+        <v>6.427679863918456e-07</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.578893665689975e-05</v>
+        <v>6.186841119415476e-07</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.0002903149579651654</v>
+        <v>1.137914978244225e-06</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.0002992796071339399</v>
+        <v>1.311314008489717e-06</v>
       </c>
       <c r="BF12" t="n">
-        <v>9.877493721432984e-05</v>
+        <v>2.303259634572896e-06</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.000282326975138858</v>
+        <v>1.731100155666354e-06</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.0002185789489885792</v>
+        <v>1.686076274154402e-07</v>
       </c>
       <c r="BI12" t="n">
-        <v>5.221756873652339e-05</v>
+        <v>7.477868848582148e-07</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.0002228934463346377</v>
+        <v>4.259712113707792e-06</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.0003162974899169058</v>
+        <v>4.206711423648812e-08</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.0001090959849534556</v>
+        <v>7.330048390485899e-08</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.0001654686639085412</v>
+        <v>2.32239881370333e-06</v>
       </c>
       <c r="BN12" t="n">
-        <v>4.707854895968921e-05</v>
+        <v>7.285259471245809e-07</v>
       </c>
       <c r="BO12" t="n">
-        <v>8.407361747231334e-05</v>
+        <v>1.977221018023556e-06</v>
       </c>
       <c r="BP12" t="n">
-        <v>8.476828952552751e-05</v>
+        <v>1.441351173525618e-06</v>
       </c>
       <c r="BQ12" t="n">
-        <v>2.976757787109818e-05</v>
+        <v>8.206473012251081e-07</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.0001225361338583753</v>
+        <v>1.970964149222709e-06</v>
       </c>
       <c r="BS12" t="n">
-        <v>2.372489143454004e-05</v>
+        <v>1.100851250157575e-06</v>
       </c>
       <c r="BT12" t="n">
-        <v>8.294339932035655e-05</v>
+        <v>1.889286750156316e-06</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.47357417922467e-05</v>
+        <v>2.328087873593176e-07</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.0006513716070912778</v>
+        <v>3.262189466113341e-06</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.0001497179036960006</v>
+        <v>7.506096153520048e-07</v>
       </c>
       <c r="BX12" t="n">
-        <v>8.579660061514005e-05</v>
+        <v>1.223093363478256e-06</v>
       </c>
       <c r="BY12" t="n">
-        <v>7.057842594804242e-05</v>
+        <v>1.550179490550363e-06</v>
       </c>
       <c r="BZ12" t="n">
-        <v>8.509851795679424e-06</v>
+        <v>3.292037717983476e-06</v>
       </c>
       <c r="CA12" t="n">
-        <v>5.072478234069422e-05</v>
+        <v>5.93773108903406e-07</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.524679414113052e-06</v>
+        <v>1.619275508346618e-06</v>
       </c>
       <c r="CC12" t="n">
-        <v>4.377466029836796e-05</v>
+        <v>3.921083191471553e-08</v>
       </c>
       <c r="CD12" t="n">
-        <v>8.167060877894983e-05</v>
+        <v>6.817296593908395e-08</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.0003189050767105073</v>
+        <v>1.539155846330686e-06</v>
       </c>
       <c r="CF12" t="n">
-        <v>6.631863652728498e-05</v>
+        <v>3.818142886302667e-07</v>
       </c>
       <c r="CG12" t="n">
-        <v>4.623439235729165e-05</v>
+        <v>9.637009270591079e-07</v>
       </c>
       <c r="CH12" t="n">
-        <v>6.810612831031904e-05</v>
+        <v>8.825053328109789e-07</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.166157835541526e-05</v>
+        <v>2.222833472842467e-06</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.0001224772859131917</v>
+        <v>6.137962600405444e-07</v>
       </c>
       <c r="CK12" t="n">
-        <v>5.08287557750009e-05</v>
+        <v>3.518284188430698e-07</v>
       </c>
       <c r="CL12" t="n">
-        <v>8.686283399583772e-05</v>
+        <v>8.774790671850496e-07</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.0004538365465123206</v>
+        <v>5.230546662460256e-08</v>
       </c>
       <c r="CN12" t="n">
-        <v>6.880261935293674e-05</v>
+        <v>3.010694854310714e-06</v>
       </c>
       <c r="CO12" t="n">
-        <v>7.271065260283649e-05</v>
+        <v>2.52499125963368e-06</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.0005464509013108909</v>
+        <v>4.111414909857558e-06</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.0003382407012395561</v>
+        <v>7.907331109890947e-07</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.0004243392031639814</v>
+        <v>1.965241608559154e-06</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.0003089748206548393</v>
+        <v>5.525971573661081e-07</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.0001630076149012893</v>
+        <v>1.867475816652586e-06</v>
       </c>
       <c r="CU12" t="n">
-        <v>0.0002466056030243635</v>
+        <v>4.395261328227207e-07</v>
       </c>
       <c r="CV12" t="n">
-        <v>7.479024498024955e-05</v>
+        <v>2.268551355655291e-07</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.0003035457921214402</v>
+        <v>1.296880554946256e-06</v>
       </c>
       <c r="CX12" t="n">
-        <v>6.857843982288614e-05</v>
+        <v>4.113815634809725e-07</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.0001324387994827703</v>
+        <v>1.352280833089026e-06</v>
       </c>
       <c r="CZ12" t="n">
-        <v>9.321765537606552e-05</v>
+        <v>9.975418606700259e-07</v>
       </c>
       <c r="DA12" t="n">
-        <v>3.159762491122819e-05</v>
+        <v>2.628138872751151e-06</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.0001223819999722764</v>
+        <v>1.381135206202089e-09</v>
       </c>
       <c r="DC12" t="n">
-        <v>9.424450399819762e-05</v>
+        <v>2.94321893079541e-07</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.0001018870752886869</v>
+        <v>5.485295559992664e-07</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.0001602504344191402</v>
+        <v>3.065380838052079e-07</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.0002697846502996981</v>
+        <v>2.980675617436646e-06</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.0001060251670423895</v>
+        <v>1.428810946890735e-06</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.0002537966065574437</v>
+        <v>9.656830002313654e-08</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.0005414252518676221</v>
+        <v>1.950915248016827e-06</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.0007134765619412065</v>
+        <v>2.240873754999484e-06</v>
       </c>
       <c r="DK12" t="n">
-        <v>6.012119411025196e-05</v>
+        <v>8.315998911712086e-07</v>
       </c>
       <c r="DL12" t="n">
-        <v>9.285258420277387e-05</v>
+        <v>4.079189466210664e-07</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.0004017963947262615</v>
+        <v>8.594325890953769e-07</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.0001132622419390827</v>
+        <v>4.153641555149079e-07</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.0001103864924516529</v>
+        <v>2.482081811194803e-07</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.0001525800325907767</v>
+        <v>5.82933012083231e-07</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.0001601546246092767</v>
+        <v>5.600585382126155e-07</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.784319313941523e-05</v>
+        <v>3.761632569876383e-07</v>
       </c>
       <c r="DS12" t="n">
-        <v>8.210854139178991e-05</v>
+        <v>1.434299576885678e-07</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.0002380119840381667</v>
+        <v>1.502299028288689e-06</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.0001968070573639125</v>
+        <v>2.710315811782493e-06</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.0001036545509123243</v>
+        <v>4.086997762442479e-07</v>
       </c>
       <c r="DW12" t="n">
-        <v>4.389646710478701e-05</v>
+        <v>4.012409817732987e-07</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.0002336534962523729</v>
+        <v>5.699266125702707e-07</v>
       </c>
       <c r="DY12" t="n">
-        <v>6.561427289852872e-05</v>
+        <v>7.213426442831405e-07</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.0002411552704870701</v>
+        <v>2.286475819346379e-06</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.000179271912202239</v>
+        <v>1.259161081179627e-06</v>
       </c>
       <c r="EB12" t="n">
-        <v>6.672294693998992e-05</v>
+        <v>1.215090833284194e-06</v>
       </c>
       <c r="EC12" t="n">
-        <v>3.868046042043716e-05</v>
+        <v>6.004449915053556e-08</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.0001862592907855287</v>
+        <v>1.30082480609417e-06</v>
       </c>
       <c r="EE12" t="n">
-        <v>0.0003856640250887722</v>
+        <v>2.496816705388483e-06</v>
       </c>
       <c r="EF12" t="n">
-        <v>0.0002549297641962767</v>
+        <v>1.703787262385958e-07</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.0004440037009771913</v>
+        <v>7.792694418640167e-07</v>
       </c>
       <c r="EH12" t="n">
-        <v>2.573709934949875e-05</v>
+        <v>7.194722684289445e-07</v>
       </c>
       <c r="EI12" t="n">
-        <v>1.034650631481782e-05</v>
+        <v>5.608408741863968e-07</v>
       </c>
       <c r="EJ12" t="n">
-        <v>4.685897238232428e-06</v>
+        <v>9.080452514353965e-07</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.0002432379842502996</v>
+        <v>1.606322939551319e-06</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.000168841754202731</v>
+        <v>5.279367201183049e-07</v>
       </c>
       <c r="EM12" t="n">
-        <v>9.037042764248326e-05</v>
+        <v>3.415898675029894e-07</v>
       </c>
       <c r="EN12" t="n">
-        <v>2.785430297080893e-05</v>
+        <v>1.324608405184335e-07</v>
       </c>
       <c r="EO12" t="n">
-        <v>8.689709648024291e-05</v>
+        <v>4.805992261935899e-07</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.0001167322843684815</v>
+        <v>2.043582526312093e-06</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.0001265308383153751</v>
+        <v>1.157423412223579e-06</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.0001812790287658572</v>
+        <v>6.484280561380729e-07</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.0001911258441396058</v>
+        <v>2.65766459506267e-07</v>
       </c>
       <c r="ET12" t="n">
-        <v>1.449551928089932e-05</v>
+        <v>1.72747377291671e-06</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.000333867414155975</v>
+        <v>9.894220056594349e-07</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.0002429642336210236</v>
+        <v>3.351842678966932e-07</v>
       </c>
       <c r="EW12" t="n">
-        <v>0.0001060033100657165</v>
+        <v>6.103690566305886e-07</v>
       </c>
       <c r="EX12" t="n">
-        <v>9.93850699160248e-05</v>
+        <v>2.63361073393753e-07</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.0003124684153590351</v>
+        <v>2.125008450093446e-06</v>
       </c>
       <c r="EZ12" t="n">
-        <v>5.056027293903753e-05</v>
+        <v>1.711809005655596e-07</v>
       </c>
       <c r="FA12" t="n">
-        <v>2.398886499577202e-05</v>
+        <v>1.616353529243497e-06</v>
       </c>
       <c r="FB12" t="n">
-        <v>6.406837928807363e-05</v>
+        <v>7.178064151958097e-07</v>
       </c>
       <c r="FC12" t="n">
-        <v>9.515457350062206e-06</v>
+        <v>2.286097696924116e-06</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.0001864988298621029</v>
+        <v>5.653748758049915e-07</v>
       </c>
       <c r="FE12" t="n">
-        <v>7.94623265392147e-05</v>
+        <v>1.38033925622949e-07</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.0001460718340240419</v>
+        <v>1.819516910472885e-07</v>
       </c>
       <c r="FG12" t="n">
-        <v>9.368343307869509e-05</v>
+        <v>1.619992673340676e-07</v>
       </c>
       <c r="FH12" t="n">
-        <v>9.774856880540028e-05</v>
+        <v>1.995362936213496e-06</v>
       </c>
       <c r="FI12" t="n">
-        <v>0.0001715690596029162</v>
+        <v>1.335662318524555e-06</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.0002771826984826475</v>
+        <v>1.018633497551491e-06</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.0001200075348606333</v>
+        <v>2.397688149358146e-06</v>
       </c>
       <c r="FL12" t="n">
-        <v>3.753237979253754e-05</v>
+        <v>2.278970214319997e-06</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.0001360860042041168</v>
+        <v>1.277662249776768e-06</v>
       </c>
       <c r="FN12" t="n">
-        <v>7.71599734434858e-05</v>
+        <v>1.766970285643765e-06</v>
       </c>
       <c r="FO12" t="n">
-        <v>0.0001498602796345949</v>
+        <v>2.901727384596597e-06</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.0002710186818148941</v>
+        <v>5.705722969651106e-07</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.0001263443264178932</v>
+        <v>5.009051733395609e-07</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.0002092294016620144</v>
+        <v>2.896080559366965e-06</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.0002723265788517892</v>
+        <v>1.40922225000395e-06</v>
       </c>
       <c r="FT12" t="n">
-        <v>3.111476326012053e-05</v>
+        <v>3.967805696447613e-06</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.0002428536681691185</v>
+        <v>6.030808208379312e-08</v>
       </c>
       <c r="FV12" t="n">
-        <v>7.982909301063046e-05</v>
+        <v>1.474039947879646e-07</v>
       </c>
       <c r="FW12" t="n">
-        <v>8.873403203324415e-07</v>
+        <v>4.079403879586607e-06</v>
       </c>
       <c r="FX12" t="n">
-        <v>8.96219426067546e-05</v>
+        <v>1.870885739663208e-07</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.0003071661340072751</v>
+        <v>6.232333475963969e-07</v>
       </c>
       <c r="FZ12" t="n">
-        <v>8.165003237081692e-05</v>
+        <v>1.641509925320861e-06</v>
       </c>
       <c r="GA12" t="n">
-        <v>6.751508772140369e-05</v>
+        <v>2.432717565170606e-06</v>
       </c>
       <c r="GB12" t="n">
-        <v>1.665238960413262e-05</v>
+        <v>6.315553946478758e-08</v>
       </c>
       <c r="GC12" t="n">
-        <v>9.690553997643292e-05</v>
+        <v>3.058127049371251e-06</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.0001629586913622916</v>
+        <v>2.686270363483345e-06</v>
       </c>
       <c r="GE12" t="n">
-        <v>1.806791988201439e-05</v>
+        <v>2.506860141693323e-07</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.0001598936360096559</v>
+        <v>6.981475735301501e-07</v>
       </c>
       <c r="GG12" t="n">
-        <v>0.0001296707923756912</v>
+        <v>7.436117925863073e-07</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.00167021865490824</v>
+        <v>0.0002845706476364285</v>
       </c>
       <c r="B13" t="n">
-        <v>9.457235137233511e-05</v>
+        <v>4.116450145374984e-05</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0001039326598402113</v>
+        <v>0.0003513158881105483</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0004113095346838236</v>
+        <v>4.370500391814858e-06</v>
       </c>
       <c r="E13" t="n">
-        <v>8.604559843661264e-05</v>
+        <v>0.0002429278974886984</v>
       </c>
       <c r="F13" t="n">
-        <v>0.001741273095831275</v>
+        <v>0.0001889189588837326</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0002676239528227597</v>
+        <v>0.0001904700766317546</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0008560880087316036</v>
+        <v>9.807941387407482e-05</v>
       </c>
       <c r="I13" t="n">
-        <v>3.276838469901122e-05</v>
+        <v>5.51759876543656e-05</v>
       </c>
       <c r="J13" t="n">
-        <v>0.001234577037394047</v>
+        <v>0.0002218269655713812</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0001699691492831334</v>
+        <v>0.0001012149587040767</v>
       </c>
       <c r="L13" t="n">
-        <v>2.443724952172488e-05</v>
+        <v>0.000335507036652416</v>
       </c>
       <c r="M13" t="n">
-        <v>0.000219470530282706</v>
+        <v>4.957719647791237e-05</v>
       </c>
       <c r="N13" t="n">
-        <v>0.000489481317345053</v>
+        <v>0.0002134509268216789</v>
       </c>
       <c r="O13" t="n">
-        <v>0.001377980457618833</v>
+        <v>0.0003517789882607758</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0006541566690430045</v>
+        <v>0.0001557462674099952</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.000984865939244628</v>
+        <v>7.422069029416889e-05</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0001051660001394339</v>
+        <v>6.483511242549866e-05</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0001898791088024154</v>
+        <v>9.546357614453882e-05</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0005104299052618444</v>
+        <v>0.0002309273986611515</v>
       </c>
       <c r="U13" t="n">
-        <v>3.203335654688999e-05</v>
+        <v>0.0001406455994583666</v>
       </c>
       <c r="V13" t="n">
-        <v>0.0004628211027011275</v>
+        <v>0.0001050041464623064</v>
       </c>
       <c r="W13" t="n">
-        <v>0.0006969345267862082</v>
+        <v>0.0001612154010217637</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0003153313009534031</v>
+        <v>0.0001811901020118967</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.0003236066550016403</v>
+        <v>6.176505848998204e-05</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.0001597583468537778</v>
+        <v>2.815273910528049e-05</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.049503958318383e-05</v>
+        <v>2.70626405836083e-05</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.0003404128656256944</v>
+        <v>5.058411989011802e-05</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.0003432836092542857</v>
+        <v>9.519295417703688e-05</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.0001445720554329455</v>
+        <v>2.093514922307804e-06</v>
       </c>
       <c r="AE13" t="n">
-        <v>9.105939534492791e-05</v>
+        <v>4.054516466567293e-06</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.436747697880492e-05</v>
+        <v>5.25549694430083e-07</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.0002059012185782194</v>
+        <v>4.096018892596476e-05</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.703036105027422e-05</v>
+        <v>8.404911932302639e-05</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.0002679356839507818</v>
+        <v>2.126984327333048e-05</v>
       </c>
       <c r="AJ13" t="n">
-        <v>4.354572593001649e-05</v>
+        <v>4.749907020595856e-05</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.0003242402744945139</v>
+        <v>1.497523044236004e-05</v>
       </c>
       <c r="AL13" t="n">
-        <v>6.94378322805278e-05</v>
+        <v>0.0001532843452878296</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.000275331549346447</v>
+        <v>6.919736188137904e-05</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.000114569251309149</v>
+        <v>6.246727571124211e-05</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.0001353005063720047</v>
+        <v>5.806615081382915e-05</v>
       </c>
       <c r="AP13" t="n">
-        <v>3.333595668664202e-05</v>
+        <v>2.330707502551377e-05</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.0001418007013853639</v>
+        <v>7.192896009655669e-05</v>
       </c>
       <c r="AR13" t="n">
-        <v>7.619181269546971e-05</v>
+        <v>5.161129956832156e-05</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.997238905460108e-05</v>
+        <v>4.475112655200064e-05</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.0009070850792340934</v>
+        <v>2.136469083779957e-05</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.000221832815441303</v>
+        <v>3.331449261168018e-05</v>
       </c>
       <c r="AV13" t="n">
-        <v>8.402916137129068e-06</v>
+        <v>0.0001664221053943038</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.0004851377452723682</v>
+        <v>7.248120527947322e-05</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.001159089268185198</v>
+        <v>7.020934572210535e-05</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.0007836536387912929</v>
+        <v>0.0001953776954906061</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.000214110070373863</v>
+        <v>5.746536407968961e-05</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.0004195109358988702</v>
+        <v>0.0001765969209372997</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.156238719588146e-05</v>
+        <v>6.356993981171399e-05</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.000372301583411172</v>
+        <v>0.0002097870601573959</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.0001624443248147145</v>
+        <v>7.369628292508423e-05</v>
       </c>
       <c r="BE13" t="n">
-        <v>9.064738696906716e-05</v>
+        <v>4.100907972315326e-06</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.000129853084217757</v>
+        <v>2.306440728716552e-05</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.0003903942997567356</v>
+        <v>6.98645890224725e-05</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.0003902594035025686</v>
+        <v>9.912991663441062e-05</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.0003353790671098977</v>
+        <v>7.871654815971851e-05</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.0004055915051139891</v>
+        <v>0.000183473268407397</v>
       </c>
       <c r="BK13" t="n">
-        <v>3.783356805797666e-05</v>
+        <v>1.36747785290936e-05</v>
       </c>
       <c r="BL13" t="n">
-        <v>2.205625605711248e-05</v>
+        <v>0.0001067290431819856</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.0002696837473195046</v>
+        <v>8.782050281297415e-05</v>
       </c>
       <c r="BN13" t="n">
-        <v>9.568194218445569e-05</v>
+        <v>0.0001613433560123667</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.0004294213431421667</v>
+        <v>0.0001256528194062412</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.0003837457334157079</v>
+        <v>0.0001683606387814507</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.100034857401624e-05</v>
+        <v>1.770026574376971e-05</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.0003631241852417588</v>
+        <v>1.418005194864236e-05</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.0004840173642151058</v>
+        <v>5.979699926683679e-05</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.000231667043408379</v>
+        <v>2.733158544288017e-05</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.0004505117249209434</v>
+        <v>3.774874494411051e-05</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.000261965295067057</v>
+        <v>0.000199053916730918</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.000180715651367791</v>
+        <v>0.0001503590756328776</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.0002590147196315229</v>
+        <v>7.558496145065874e-05</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.0005098658730275929</v>
+        <v>0.0001156370781245641</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.000585670059081167</v>
+        <v>0.000233451573876664</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.707853804575279e-05</v>
+        <v>7.526332410634495e-06</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.0001970465818885714</v>
+        <v>2.223123556177597e-05</v>
       </c>
       <c r="CC13" t="n">
-        <v>1.544131737318821e-05</v>
+        <v>3.954645217163488e-05</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.0003249882720410824</v>
+        <v>6.48438508505933e-05</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.0002376708289375529</v>
+        <v>0.0001357399742119014</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.394972034380771e-05</v>
+        <v>7.506688416469842e-05</v>
       </c>
       <c r="CG13" t="n">
-        <v>1.570706444908865e-05</v>
+        <v>8.179075666703284e-05</v>
       </c>
       <c r="CH13" t="n">
-        <v>3.818058030446991e-05</v>
+        <v>5.263241473585367e-05</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.0002575337130110711</v>
+        <v>5.190487354411744e-05</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2.672460686881095e-05</v>
+        <v>4.671094757213723e-06</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.0003021221491508186</v>
+        <v>3.474405821179971e-05</v>
       </c>
       <c r="CL13" t="n">
-        <v>3.335371002322063e-05</v>
+        <v>2.136584225809202e-05</v>
       </c>
       <c r="CM13" t="n">
-        <v>3.04564819089137e-05</v>
+        <v>2.517998109397013e-05</v>
       </c>
       <c r="CN13" t="n">
-        <v>8.544472802896053e-05</v>
+        <v>6.703023245790973e-05</v>
       </c>
       <c r="CO13" t="n">
-        <v>5.306265666149557e-05</v>
+        <v>7.228417962323874e-05</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.838301043084357e-05</v>
+        <v>4.121501842746511e-05</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.0007699021953158081</v>
+        <v>6.838799163233489e-05</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.0001226038439199328</v>
+        <v>3.489452501526102e-05</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.0002251061087008566</v>
+        <v>0.0001264276797883213</v>
       </c>
       <c r="CT13" t="n">
-        <v>6.472003587987274e-05</v>
+        <v>4.855604493059218e-05</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.0001393267011735588</v>
+        <v>1.282876110053621e-05</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.0002993880480062217</v>
+        <v>6.743473204551265e-05</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.0002217972651124001</v>
+        <v>9.504622721578926e-05</v>
       </c>
       <c r="CX13" t="n">
-        <v>4.503293166635558e-05</v>
+        <v>6.342241249512881e-05</v>
       </c>
       <c r="CY13" t="n">
-        <v>9.8626253020484e-05</v>
+        <v>7.703118171775714e-05</v>
       </c>
       <c r="CZ13" t="n">
-        <v>3.361049311934039e-05</v>
+        <v>4.523683310253546e-05</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.0002509529876988381</v>
+        <v>5.475396028487012e-05</v>
       </c>
       <c r="DB13" t="n">
-        <v>9.168230462819338e-06</v>
+        <v>2.578637941041961e-05</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.000317820260534063</v>
+        <v>1.031508782034507e-05</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.331703944946639e-05</v>
+        <v>9.382628377352376e-06</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.0001015603847918101</v>
+        <v>8.372783486265689e-05</v>
       </c>
       <c r="DF13" t="n">
-        <v>4.186153091723099e-06</v>
+        <v>2.029938332270831e-05</v>
       </c>
       <c r="DG13" t="n">
-        <v>8.462984260404482e-05</v>
+        <v>8.753647853154689e-05</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.0002712910354603082</v>
+        <v>9.287933062296361e-05</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.001021156320348382</v>
+        <v>0.0001209652400575578</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.0001048705671564676</v>
+        <v>6.690370355499908e-05</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.082425923319533e-05</v>
+        <v>3.196422039764002e-05</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.0004910093848593533</v>
+        <v>3.395717430976219e-05</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.0003435872786212713</v>
+        <v>1.992621764657088e-05</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.0001932077575474977</v>
+        <v>3.052259125979617e-05</v>
       </c>
       <c r="DO13" t="n">
-        <v>9.108742233365774e-05</v>
+        <v>5.519985643331893e-05</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.0001477284531574696</v>
+        <v>0.0001550452725496143</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.0002956194803118706</v>
+        <v>0.0001169196766568348</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.0002545712632127106</v>
+        <v>4.054810415254906e-05</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.0002335230819880962</v>
+        <v>0.0001163043634733185</v>
       </c>
       <c r="DT13" t="n">
-        <v>1.033703301800415e-05</v>
+        <v>4.192177584627643e-05</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.0004397512238938361</v>
+        <v>7.888139407441486e-06</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.0001359848247375339</v>
+        <v>7.391051894956036e-06</v>
       </c>
       <c r="DW13" t="n">
-        <v>2.156382834073156e-06</v>
+        <v>4.963086030329578e-05</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.000174379616510123</v>
+        <v>4.447580795385875e-05</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.831164450384676e-06</v>
+        <v>0.0002256112347822636</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.0001053648957167752</v>
+        <v>0.0001201660998049192</v>
       </c>
       <c r="EA13" t="n">
-        <v>6.966355431359261e-05</v>
+        <v>2.728130129980855e-05</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.0004054703167639673</v>
+        <v>0.0001241442805621773</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.0002119124983437359</v>
+        <v>2.072961251542438e-05</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.000367523287422955</v>
+        <v>2.55653740168782e-05</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.0001539886288810521</v>
+        <v>1.925789547385648e-06</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.0002663191989995539</v>
+        <v>3.364745498402044e-05</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.0004039595078211278</v>
+        <v>0.0001899069757200778</v>
       </c>
       <c r="EH13" t="n">
-        <v>1.525594143458875e-05</v>
+        <v>1.849455293267965e-05</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.0001829966640798375</v>
+        <v>5.304724982124753e-05</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.0001377759617753327</v>
+        <v>0.0001031080755637959</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.0001358421868644655</v>
+        <v>6.546754775627051e-06</v>
       </c>
       <c r="EL13" t="n">
-        <v>4.225572774885222e-05</v>
+        <v>2.999361277034041e-05</v>
       </c>
       <c r="EM13" t="n">
-        <v>1.93957475858042e-05</v>
+        <v>4.254993109498173e-05</v>
       </c>
       <c r="EN13" t="n">
-        <v>6.253326864680275e-05</v>
+        <v>3.496760837151669e-05</v>
       </c>
       <c r="EO13" t="n">
-        <v>9.829392365645617e-05</v>
+        <v>4.722438825410791e-05</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.0003070847596973181</v>
+        <v>0.0001221645652549341</v>
       </c>
       <c r="EQ13" t="n">
-        <v>7.616166840307415e-05</v>
+        <v>6.350100011331961e-05</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.000132653716718778</v>
+        <v>1.293811146751978e-05</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.0004557844949886203</v>
+        <v>3.061180905206129e-05</v>
       </c>
       <c r="ET13" t="n">
-        <v>8.481410623062402e-05</v>
+        <v>0.0001446355890948325</v>
       </c>
       <c r="EU13" t="n">
-        <v>2.369064895901829e-05</v>
+        <v>4.393735434859991e-05</v>
       </c>
       <c r="EV13" t="n">
-        <v>6.031319935573265e-05</v>
+        <v>0.0001642536517465487</v>
       </c>
       <c r="EW13" t="n">
-        <v>2.31600170081947e-05</v>
+        <v>4.494047607295215e-05</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.0002573538513388485</v>
+        <v>5.405039701145142e-05</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.0001832035486586392</v>
+        <v>9.381685958942398e-05</v>
       </c>
       <c r="EZ13" t="n">
-        <v>4.149982851231471e-05</v>
+        <v>5.841600795974955e-05</v>
       </c>
       <c r="FA13" t="n">
-        <v>7.206894224509597e-05</v>
+        <v>9.20398160815239e-05</v>
       </c>
       <c r="FB13" t="n">
-        <v>7.042604556772858e-05</v>
+        <v>6.559869507327676e-05</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.0002192361571360379</v>
+        <v>8.444026752840728e-05</v>
       </c>
       <c r="FD13" t="n">
-        <v>5.375863838708028e-05</v>
+        <v>1.181417610496283e-05</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.0004133410402573645</v>
+        <v>4.956786142429337e-06</v>
       </c>
       <c r="FF13" t="n">
-        <v>5.782567313872278e-07</v>
+        <v>3.482586180325598e-06</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.0001954740146175027</v>
+        <v>0.0001010437117656693</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.0002578626153990626</v>
+        <v>5.009950837120414e-05</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.000141154756420292</v>
+        <v>3.099008608842269e-05</v>
       </c>
       <c r="FJ13" t="n">
-        <v>6.83922553434968e-05</v>
+        <v>6.718456279486418e-05</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.0001891303836600855</v>
+        <v>0.000169078863109462</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.0002186479250667617</v>
+        <v>0.0001702331937849522</v>
       </c>
       <c r="FM13" t="n">
-        <v>5.577541378443129e-05</v>
+        <v>5.207703361520544e-05</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.0001239460834767669</v>
+        <v>0.000123813355457969</v>
       </c>
       <c r="FO13" t="n">
-        <v>6.068305083317682e-06</v>
+        <v>5.254218922345899e-05</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.0001530023582745343</v>
+        <v>3.392765938770026e-05</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.00013038631004747</v>
+        <v>0.0002019608800765127</v>
       </c>
       <c r="FR13" t="n">
-        <v>1.128824078477919e-05</v>
+        <v>0.0002510814229026437</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.0004744056495837867</v>
+        <v>2.407183637842536e-05</v>
       </c>
       <c r="FT13" t="n">
-        <v>2.861343455151655e-05</v>
+        <v>0.0003400120476726443</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.0004335285630077124</v>
+        <v>5.441458051791415e-05</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.000273186044069007</v>
+        <v>0.0002336479956284165</v>
       </c>
       <c r="FW13" t="n">
-        <v>5.068710379418917e-05</v>
+        <v>8.208354120142758e-05</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.0001207228560815565</v>
+        <v>0.00012780494580511</v>
       </c>
       <c r="FY13" t="n">
-        <v>7.045459642540663e-05</v>
+        <v>3.680904046632349e-05</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.0002105933090206236</v>
+        <v>5.894929927308112e-05</v>
       </c>
       <c r="GA13" t="n">
-        <v>2.326890535186976e-05</v>
+        <v>0.0001227341126650572</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.0001587430451763794</v>
+        <v>4.456578244571574e-05</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.0001496007316745818</v>
+        <v>3.791035123867914e-05</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.0003080392198171467</v>
+        <v>5.053302811575122e-05</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.0002867106813937426</v>
+        <v>4.514684769674204e-05</v>
       </c>
       <c r="GF13" t="n">
-        <v>4.808702215086669e-06</v>
+        <v>0.0002294382429681718</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.0001312531239818782</v>
+        <v>6.806275632698089e-05</v>
       </c>
     </row>
   </sheetData>
